--- a/Files/Madden26/IE/Season2/FreeAgency/Output/ContractOffer[].xlsx
+++ b/Files/Madden26/IE/Season2/FreeAgency/Output/ContractOffer[].xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,4652 +429,4652 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer0</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer3</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer4</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer5</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer6</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer7</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer8</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer9</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer10</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer11</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer12</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer13</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer14</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer15</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer16</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer17</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer18</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer19</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer20</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer21</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer22</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer23</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer24</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer25</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer26</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer27</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer28</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer29</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer30</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer31</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer32</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer33</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer34</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer35</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer36</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer37</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer38</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer39</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer40</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer41</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer42</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer43</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer44</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer45</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer46</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer47</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer48</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer49</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer50</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer51</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer52</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer53</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer54</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer55</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer56</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer57</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer58</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer59</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer60</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer61</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer62</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer63</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer64</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer65</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer66</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer67</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer68</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer69</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer70</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer71</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer72</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer73</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer74</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer75</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer76</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer77</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer78</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer79</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer80</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer81</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer82</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer83</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer84</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer85</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer86</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer87</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer88</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer89</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer90</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer91</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer92</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer93</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer94</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer95</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer96</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer97</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer98</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer99</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer100</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer101</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer102</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer103</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer104</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer105</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer106</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer107</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer108</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer109</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer110</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer111</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer112</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer113</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer114</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer115</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer116</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer117</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer118</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer119</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer120</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer121</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer122</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer123</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer124</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer125</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer126</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer127</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer128</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer129</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer130</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer131</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer132</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer133</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer134</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer135</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer136</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer137</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer138</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer139</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer140</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer141</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer142</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer143</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer144</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer145</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer146</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer147</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer148</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer149</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer150</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer151</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer152</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer153</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer154</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer155</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer156</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer157</t>
         </is>
       </c>
-      <c r="FC1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer158</t>
         </is>
       </c>
-      <c r="FD1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer159</t>
         </is>
       </c>
-      <c r="FE1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer160</t>
         </is>
       </c>
-      <c r="FF1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer161</t>
         </is>
       </c>
-      <c r="FG1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer162</t>
         </is>
       </c>
-      <c r="FH1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer163</t>
         </is>
       </c>
-      <c r="FI1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer164</t>
         </is>
       </c>
-      <c r="FJ1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer165</t>
         </is>
       </c>
-      <c r="FK1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer166</t>
         </is>
       </c>
-      <c r="FL1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer167</t>
         </is>
       </c>
-      <c r="FM1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer168</t>
         </is>
       </c>
-      <c r="FN1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer169</t>
         </is>
       </c>
-      <c r="FO1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer170</t>
         </is>
       </c>
-      <c r="FP1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer171</t>
         </is>
       </c>
-      <c r="FQ1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer172</t>
         </is>
       </c>
-      <c r="FR1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer173</t>
         </is>
       </c>
-      <c r="FS1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer174</t>
         </is>
       </c>
-      <c r="FT1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer175</t>
         </is>
       </c>
-      <c r="FU1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer176</t>
         </is>
       </c>
-      <c r="FV1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer177</t>
         </is>
       </c>
-      <c r="FW1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer178</t>
         </is>
       </c>
-      <c r="FX1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer179</t>
         </is>
       </c>
-      <c r="FY1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer180</t>
         </is>
       </c>
-      <c r="FZ1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer181</t>
         </is>
       </c>
-      <c r="GA1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer182</t>
         </is>
       </c>
-      <c r="GB1" t="inlineStr">
+      <c r="GB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer183</t>
         </is>
       </c>
-      <c r="GC1" t="inlineStr">
+      <c r="GC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer184</t>
         </is>
       </c>
-      <c r="GD1" t="inlineStr">
+      <c r="GD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer185</t>
         </is>
       </c>
-      <c r="GE1" t="inlineStr">
+      <c r="GE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer186</t>
         </is>
       </c>
-      <c r="GF1" t="inlineStr">
+      <c r="GF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer187</t>
         </is>
       </c>
-      <c r="GG1" t="inlineStr">
+      <c r="GG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer188</t>
         </is>
       </c>
-      <c r="GH1" t="inlineStr">
+      <c r="GH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer189</t>
         </is>
       </c>
-      <c r="GI1" t="inlineStr">
+      <c r="GI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer190</t>
         </is>
       </c>
-      <c r="GJ1" t="inlineStr">
+      <c r="GJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer191</t>
         </is>
       </c>
-      <c r="GK1" t="inlineStr">
+      <c r="GK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer192</t>
         </is>
       </c>
-      <c r="GL1" t="inlineStr">
+      <c r="GL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer193</t>
         </is>
       </c>
-      <c r="GM1" t="inlineStr">
+      <c r="GM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer194</t>
         </is>
       </c>
-      <c r="GN1" t="inlineStr">
+      <c r="GN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer195</t>
         </is>
       </c>
-      <c r="GO1" t="inlineStr">
+      <c r="GO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer196</t>
         </is>
       </c>
-      <c r="GP1" t="inlineStr">
+      <c r="GP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer197</t>
         </is>
       </c>
-      <c r="GQ1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer198</t>
         </is>
       </c>
-      <c r="GR1" t="inlineStr">
+      <c r="GR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer199</t>
         </is>
       </c>
-      <c r="GS1" t="inlineStr">
+      <c r="GS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer200</t>
         </is>
       </c>
-      <c r="GT1" t="inlineStr">
+      <c r="GT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer201</t>
         </is>
       </c>
-      <c r="GU1" t="inlineStr">
+      <c r="GU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer202</t>
         </is>
       </c>
-      <c r="GV1" t="inlineStr">
+      <c r="GV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer203</t>
         </is>
       </c>
-      <c r="GW1" t="inlineStr">
+      <c r="GW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer204</t>
         </is>
       </c>
-      <c r="GX1" t="inlineStr">
+      <c r="GX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer205</t>
         </is>
       </c>
-      <c r="GY1" t="inlineStr">
+      <c r="GY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer206</t>
         </is>
       </c>
-      <c r="GZ1" t="inlineStr">
+      <c r="GZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer207</t>
         </is>
       </c>
-      <c r="HA1" t="inlineStr">
+      <c r="HA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer208</t>
         </is>
       </c>
-      <c r="HB1" t="inlineStr">
+      <c r="HB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer209</t>
         </is>
       </c>
-      <c r="HC1" t="inlineStr">
+      <c r="HC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer210</t>
         </is>
       </c>
-      <c r="HD1" t="inlineStr">
+      <c r="HD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer211</t>
         </is>
       </c>
-      <c r="HE1" t="inlineStr">
+      <c r="HE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer212</t>
         </is>
       </c>
-      <c r="HF1" t="inlineStr">
+      <c r="HF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer213</t>
         </is>
       </c>
-      <c r="HG1" t="inlineStr">
+      <c r="HG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer214</t>
         </is>
       </c>
-      <c r="HH1" t="inlineStr">
+      <c r="HH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer215</t>
         </is>
       </c>
-      <c r="HI1" t="inlineStr">
+      <c r="HI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer216</t>
         </is>
       </c>
-      <c r="HJ1" t="inlineStr">
+      <c r="HJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer217</t>
         </is>
       </c>
-      <c r="HK1" t="inlineStr">
+      <c r="HK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer218</t>
         </is>
       </c>
-      <c r="HL1" t="inlineStr">
+      <c r="HL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer219</t>
         </is>
       </c>
-      <c r="HM1" t="inlineStr">
+      <c r="HM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer220</t>
         </is>
       </c>
-      <c r="HN1" t="inlineStr">
+      <c r="HN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer221</t>
         </is>
       </c>
-      <c r="HO1" t="inlineStr">
+      <c r="HO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer222</t>
         </is>
       </c>
-      <c r="HP1" t="inlineStr">
+      <c r="HP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer223</t>
         </is>
       </c>
-      <c r="HQ1" t="inlineStr">
+      <c r="HQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer224</t>
         </is>
       </c>
-      <c r="HR1" t="inlineStr">
+      <c r="HR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer225</t>
         </is>
       </c>
-      <c r="HS1" t="inlineStr">
+      <c r="HS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer226</t>
         </is>
       </c>
-      <c r="HT1" t="inlineStr">
+      <c r="HT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer227</t>
         </is>
       </c>
-      <c r="HU1" t="inlineStr">
+      <c r="HU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer228</t>
         </is>
       </c>
-      <c r="HV1" t="inlineStr">
+      <c r="HV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer229</t>
         </is>
       </c>
-      <c r="HW1" t="inlineStr">
+      <c r="HW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer230</t>
         </is>
       </c>
-      <c r="HX1" t="inlineStr">
+      <c r="HX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer231</t>
         </is>
       </c>
-      <c r="HY1" t="inlineStr">
+      <c r="HY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer232</t>
         </is>
       </c>
-      <c r="HZ1" t="inlineStr">
+      <c r="HZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer233</t>
         </is>
       </c>
-      <c r="IA1" t="inlineStr">
+      <c r="IA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer234</t>
         </is>
       </c>
-      <c r="IB1" t="inlineStr">
+      <c r="IB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer235</t>
         </is>
       </c>
-      <c r="IC1" t="inlineStr">
+      <c r="IC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer236</t>
         </is>
       </c>
-      <c r="ID1" t="inlineStr">
+      <c r="ID1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer237</t>
         </is>
       </c>
-      <c r="IE1" t="inlineStr">
+      <c r="IE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer238</t>
         </is>
       </c>
-      <c r="IF1" t="inlineStr">
+      <c r="IF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer239</t>
         </is>
       </c>
-      <c r="IG1" t="inlineStr">
+      <c r="IG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer240</t>
         </is>
       </c>
-      <c r="IH1" t="inlineStr">
+      <c r="IH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer241</t>
         </is>
       </c>
-      <c r="II1" t="inlineStr">
+      <c r="II1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer242</t>
         </is>
       </c>
-      <c r="IJ1" t="inlineStr">
+      <c r="IJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer243</t>
         </is>
       </c>
-      <c r="IK1" t="inlineStr">
+      <c r="IK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer244</t>
         </is>
       </c>
-      <c r="IL1" t="inlineStr">
+      <c r="IL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer245</t>
         </is>
       </c>
-      <c r="IM1" t="inlineStr">
+      <c r="IM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer246</t>
         </is>
       </c>
-      <c r="IN1" t="inlineStr">
+      <c r="IN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer247</t>
         </is>
       </c>
-      <c r="IO1" t="inlineStr">
+      <c r="IO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer248</t>
         </is>
       </c>
-      <c r="IP1" t="inlineStr">
+      <c r="IP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer249</t>
         </is>
       </c>
-      <c r="IQ1" t="inlineStr">
+      <c r="IQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer250</t>
         </is>
       </c>
-      <c r="IR1" t="inlineStr">
+      <c r="IR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer251</t>
         </is>
       </c>
-      <c r="IS1" t="inlineStr">
+      <c r="IS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer252</t>
         </is>
       </c>
-      <c r="IT1" t="inlineStr">
+      <c r="IT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer253</t>
         </is>
       </c>
-      <c r="IU1" t="inlineStr">
+      <c r="IU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer254</t>
         </is>
       </c>
-      <c r="IV1" t="inlineStr">
+      <c r="IV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer255</t>
         </is>
       </c>
-      <c r="IW1" t="inlineStr">
+      <c r="IW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer256</t>
         </is>
       </c>
-      <c r="IX1" t="inlineStr">
+      <c r="IX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer257</t>
         </is>
       </c>
-      <c r="IY1" t="inlineStr">
+      <c r="IY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer258</t>
         </is>
       </c>
-      <c r="IZ1" t="inlineStr">
+      <c r="IZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer259</t>
         </is>
       </c>
-      <c r="JA1" t="inlineStr">
+      <c r="JA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer260</t>
         </is>
       </c>
-      <c r="JB1" t="inlineStr">
+      <c r="JB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer261</t>
         </is>
       </c>
-      <c r="JC1" t="inlineStr">
+      <c r="JC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer262</t>
         </is>
       </c>
-      <c r="JD1" t="inlineStr">
+      <c r="JD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer263</t>
         </is>
       </c>
-      <c r="JE1" t="inlineStr">
+      <c r="JE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer264</t>
         </is>
       </c>
-      <c r="JF1" t="inlineStr">
+      <c r="JF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer265</t>
         </is>
       </c>
-      <c r="JG1" t="inlineStr">
+      <c r="JG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer266</t>
         </is>
       </c>
-      <c r="JH1" t="inlineStr">
+      <c r="JH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer267</t>
         </is>
       </c>
-      <c r="JI1" t="inlineStr">
+      <c r="JI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer268</t>
         </is>
       </c>
-      <c r="JJ1" t="inlineStr">
+      <c r="JJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer269</t>
         </is>
       </c>
-      <c r="JK1" t="inlineStr">
+      <c r="JK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer270</t>
         </is>
       </c>
-      <c r="JL1" t="inlineStr">
+      <c r="JL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer271</t>
         </is>
       </c>
-      <c r="JM1" t="inlineStr">
+      <c r="JM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer272</t>
         </is>
       </c>
-      <c r="JN1" t="inlineStr">
+      <c r="JN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer273</t>
         </is>
       </c>
-      <c r="JO1" t="inlineStr">
+      <c r="JO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer274</t>
         </is>
       </c>
-      <c r="JP1" t="inlineStr">
+      <c r="JP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer275</t>
         </is>
       </c>
-      <c r="JQ1" t="inlineStr">
+      <c r="JQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer276</t>
         </is>
       </c>
-      <c r="JR1" t="inlineStr">
+      <c r="JR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer277</t>
         </is>
       </c>
-      <c r="JS1" t="inlineStr">
+      <c r="JS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer278</t>
         </is>
       </c>
-      <c r="JT1" t="inlineStr">
+      <c r="JT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer279</t>
         </is>
       </c>
-      <c r="JU1" t="inlineStr">
+      <c r="JU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer280</t>
         </is>
       </c>
-      <c r="JV1" t="inlineStr">
+      <c r="JV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer281</t>
         </is>
       </c>
-      <c r="JW1" t="inlineStr">
+      <c r="JW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer282</t>
         </is>
       </c>
-      <c r="JX1" t="inlineStr">
+      <c r="JX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer283</t>
         </is>
       </c>
-      <c r="JY1" t="inlineStr">
+      <c r="JY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer284</t>
         </is>
       </c>
-      <c r="JZ1" t="inlineStr">
+      <c r="JZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer285</t>
         </is>
       </c>
-      <c r="KA1" t="inlineStr">
+      <c r="KA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer286</t>
         </is>
       </c>
-      <c r="KB1" t="inlineStr">
+      <c r="KB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer287</t>
         </is>
       </c>
-      <c r="KC1" t="inlineStr">
+      <c r="KC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer288</t>
         </is>
       </c>
-      <c r="KD1" t="inlineStr">
+      <c r="KD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer289</t>
         </is>
       </c>
-      <c r="KE1" t="inlineStr">
+      <c r="KE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer290</t>
         </is>
       </c>
-      <c r="KF1" t="inlineStr">
+      <c r="KF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer291</t>
         </is>
       </c>
-      <c r="KG1" t="inlineStr">
+      <c r="KG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer292</t>
         </is>
       </c>
-      <c r="KH1" t="inlineStr">
+      <c r="KH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer293</t>
         </is>
       </c>
-      <c r="KI1" t="inlineStr">
+      <c r="KI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer294</t>
         </is>
       </c>
-      <c r="KJ1" t="inlineStr">
+      <c r="KJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer295</t>
         </is>
       </c>
-      <c r="KK1" t="inlineStr">
+      <c r="KK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer296</t>
         </is>
       </c>
-      <c r="KL1" t="inlineStr">
+      <c r="KL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer297</t>
         </is>
       </c>
-      <c r="KM1" t="inlineStr">
+      <c r="KM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer298</t>
         </is>
       </c>
-      <c r="KN1" t="inlineStr">
+      <c r="KN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer299</t>
         </is>
       </c>
-      <c r="KO1" t="inlineStr">
+      <c r="KO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer300</t>
         </is>
       </c>
-      <c r="KP1" t="inlineStr">
+      <c r="KP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer301</t>
         </is>
       </c>
-      <c r="KQ1" t="inlineStr">
+      <c r="KQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer302</t>
         </is>
       </c>
-      <c r="KR1" t="inlineStr">
+      <c r="KR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer303</t>
         </is>
       </c>
-      <c r="KS1" t="inlineStr">
+      <c r="KS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer304</t>
         </is>
       </c>
-      <c r="KT1" t="inlineStr">
+      <c r="KT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer305</t>
         </is>
       </c>
-      <c r="KU1" t="inlineStr">
+      <c r="KU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer306</t>
         </is>
       </c>
-      <c r="KV1" t="inlineStr">
+      <c r="KV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer307</t>
         </is>
       </c>
-      <c r="KW1" t="inlineStr">
+      <c r="KW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer308</t>
         </is>
       </c>
-      <c r="KX1" t="inlineStr">
+      <c r="KX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer309</t>
         </is>
       </c>
-      <c r="KY1" t="inlineStr">
+      <c r="KY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer310</t>
         </is>
       </c>
-      <c r="KZ1" t="inlineStr">
+      <c r="KZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer311</t>
         </is>
       </c>
-      <c r="LA1" t="inlineStr">
+      <c r="LA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer312</t>
         </is>
       </c>
-      <c r="LB1" t="inlineStr">
+      <c r="LB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer313</t>
         </is>
       </c>
-      <c r="LC1" t="inlineStr">
+      <c r="LC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer314</t>
         </is>
       </c>
-      <c r="LD1" t="inlineStr">
+      <c r="LD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer315</t>
         </is>
       </c>
-      <c r="LE1" t="inlineStr">
+      <c r="LE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer316</t>
         </is>
       </c>
-      <c r="LF1" t="inlineStr">
+      <c r="LF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer317</t>
         </is>
       </c>
-      <c r="LG1" t="inlineStr">
+      <c r="LG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer318</t>
         </is>
       </c>
-      <c r="LH1" t="inlineStr">
+      <c r="LH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer319</t>
         </is>
       </c>
-      <c r="LI1" t="inlineStr">
+      <c r="LI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer320</t>
         </is>
       </c>
-      <c r="LJ1" t="inlineStr">
+      <c r="LJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer321</t>
         </is>
       </c>
-      <c r="LK1" t="inlineStr">
+      <c r="LK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer322</t>
         </is>
       </c>
-      <c r="LL1" t="inlineStr">
+      <c r="LL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer323</t>
         </is>
       </c>
-      <c r="LM1" t="inlineStr">
+      <c r="LM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer324</t>
         </is>
       </c>
-      <c r="LN1" t="inlineStr">
+      <c r="LN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer325</t>
         </is>
       </c>
-      <c r="LO1" t="inlineStr">
+      <c r="LO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer326</t>
         </is>
       </c>
-      <c r="LP1" t="inlineStr">
+      <c r="LP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer327</t>
         </is>
       </c>
-      <c r="LQ1" t="inlineStr">
+      <c r="LQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer328</t>
         </is>
       </c>
-      <c r="LR1" t="inlineStr">
+      <c r="LR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer329</t>
         </is>
       </c>
-      <c r="LS1" t="inlineStr">
+      <c r="LS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer330</t>
         </is>
       </c>
-      <c r="LT1" t="inlineStr">
+      <c r="LT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer331</t>
         </is>
       </c>
-      <c r="LU1" t="inlineStr">
+      <c r="LU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer332</t>
         </is>
       </c>
-      <c r="LV1" t="inlineStr">
+      <c r="LV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer333</t>
         </is>
       </c>
-      <c r="LW1" t="inlineStr">
+      <c r="LW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer334</t>
         </is>
       </c>
-      <c r="LX1" t="inlineStr">
+      <c r="LX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer335</t>
         </is>
       </c>
-      <c r="LY1" t="inlineStr">
+      <c r="LY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer336</t>
         </is>
       </c>
-      <c r="LZ1" t="inlineStr">
+      <c r="LZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer337</t>
         </is>
       </c>
-      <c r="MA1" t="inlineStr">
+      <c r="MA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer338</t>
         </is>
       </c>
-      <c r="MB1" t="inlineStr">
+      <c r="MB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer339</t>
         </is>
       </c>
-      <c r="MC1" t="inlineStr">
+      <c r="MC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer340</t>
         </is>
       </c>
-      <c r="MD1" t="inlineStr">
+      <c r="MD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer341</t>
         </is>
       </c>
-      <c r="ME1" t="inlineStr">
+      <c r="ME1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer342</t>
         </is>
       </c>
-      <c r="MF1" t="inlineStr">
+      <c r="MF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer343</t>
         </is>
       </c>
-      <c r="MG1" t="inlineStr">
+      <c r="MG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer344</t>
         </is>
       </c>
-      <c r="MH1" t="inlineStr">
+      <c r="MH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer345</t>
         </is>
       </c>
-      <c r="MI1" t="inlineStr">
+      <c r="MI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer346</t>
         </is>
       </c>
-      <c r="MJ1" t="inlineStr">
+      <c r="MJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer347</t>
         </is>
       </c>
-      <c r="MK1" t="inlineStr">
+      <c r="MK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer348</t>
         </is>
       </c>
-      <c r="ML1" t="inlineStr">
+      <c r="ML1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer349</t>
         </is>
       </c>
-      <c r="MM1" t="inlineStr">
+      <c r="MM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer350</t>
         </is>
       </c>
-      <c r="MN1" t="inlineStr">
+      <c r="MN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer351</t>
         </is>
       </c>
-      <c r="MO1" t="inlineStr">
+      <c r="MO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer352</t>
         </is>
       </c>
-      <c r="MP1" t="inlineStr">
+      <c r="MP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer353</t>
         </is>
       </c>
-      <c r="MQ1" t="inlineStr">
+      <c r="MQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer354</t>
         </is>
       </c>
-      <c r="MR1" t="inlineStr">
+      <c r="MR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer355</t>
         </is>
       </c>
-      <c r="MS1" t="inlineStr">
+      <c r="MS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer356</t>
         </is>
       </c>
-      <c r="MT1" t="inlineStr">
+      <c r="MT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer357</t>
         </is>
       </c>
-      <c r="MU1" t="inlineStr">
+      <c r="MU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer358</t>
         </is>
       </c>
-      <c r="MV1" t="inlineStr">
+      <c r="MV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer359</t>
         </is>
       </c>
-      <c r="MW1" t="inlineStr">
+      <c r="MW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer360</t>
         </is>
       </c>
-      <c r="MX1" t="inlineStr">
+      <c r="MX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer361</t>
         </is>
       </c>
-      <c r="MY1" t="inlineStr">
+      <c r="MY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer362</t>
         </is>
       </c>
-      <c r="MZ1" t="inlineStr">
+      <c r="MZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer363</t>
         </is>
       </c>
-      <c r="NA1" t="inlineStr">
+      <c r="NA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer364</t>
         </is>
       </c>
-      <c r="NB1" t="inlineStr">
+      <c r="NB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer365</t>
         </is>
       </c>
-      <c r="NC1" t="inlineStr">
+      <c r="NC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer366</t>
         </is>
       </c>
-      <c r="ND1" t="inlineStr">
+      <c r="ND1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer367</t>
         </is>
       </c>
-      <c r="NE1" t="inlineStr">
+      <c r="NE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer368</t>
         </is>
       </c>
-      <c r="NF1" t="inlineStr">
+      <c r="NF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer369</t>
         </is>
       </c>
-      <c r="NG1" t="inlineStr">
+      <c r="NG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer370</t>
         </is>
       </c>
-      <c r="NH1" t="inlineStr">
+      <c r="NH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer371</t>
         </is>
       </c>
-      <c r="NI1" t="inlineStr">
+      <c r="NI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer372</t>
         </is>
       </c>
-      <c r="NJ1" t="inlineStr">
+      <c r="NJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer373</t>
         </is>
       </c>
-      <c r="NK1" t="inlineStr">
+      <c r="NK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer374</t>
         </is>
       </c>
-      <c r="NL1" t="inlineStr">
+      <c r="NL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer375</t>
         </is>
       </c>
-      <c r="NM1" t="inlineStr">
+      <c r="NM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer376</t>
         </is>
       </c>
-      <c r="NN1" t="inlineStr">
+      <c r="NN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer377</t>
         </is>
       </c>
-      <c r="NO1" t="inlineStr">
+      <c r="NO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer378</t>
         </is>
       </c>
-      <c r="NP1" t="inlineStr">
+      <c r="NP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer379</t>
         </is>
       </c>
-      <c r="NQ1" t="inlineStr">
+      <c r="NQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer380</t>
         </is>
       </c>
-      <c r="NR1" t="inlineStr">
+      <c r="NR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer381</t>
         </is>
       </c>
-      <c r="NS1" t="inlineStr">
+      <c r="NS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer382</t>
         </is>
       </c>
-      <c r="NT1" t="inlineStr">
+      <c r="NT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer383</t>
         </is>
       </c>
-      <c r="NU1" t="inlineStr">
+      <c r="NU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer384</t>
         </is>
       </c>
-      <c r="NV1" t="inlineStr">
+      <c r="NV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer385</t>
         </is>
       </c>
-      <c r="NW1" t="inlineStr">
+      <c r="NW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer386</t>
         </is>
       </c>
-      <c r="NX1" t="inlineStr">
+      <c r="NX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer387</t>
         </is>
       </c>
-      <c r="NY1" t="inlineStr">
+      <c r="NY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer388</t>
         </is>
       </c>
-      <c r="NZ1" t="inlineStr">
+      <c r="NZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer389</t>
         </is>
       </c>
-      <c r="OA1" t="inlineStr">
+      <c r="OA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer390</t>
         </is>
       </c>
-      <c r="OB1" t="inlineStr">
+      <c r="OB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer391</t>
         </is>
       </c>
-      <c r="OC1" t="inlineStr">
+      <c r="OC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer392</t>
         </is>
       </c>
-      <c r="OD1" t="inlineStr">
+      <c r="OD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer393</t>
         </is>
       </c>
-      <c r="OE1" t="inlineStr">
+      <c r="OE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer394</t>
         </is>
       </c>
-      <c r="OF1" t="inlineStr">
+      <c r="OF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer395</t>
         </is>
       </c>
-      <c r="OG1" t="inlineStr">
+      <c r="OG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer396</t>
         </is>
       </c>
-      <c r="OH1" t="inlineStr">
+      <c r="OH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer397</t>
         </is>
       </c>
-      <c r="OI1" t="inlineStr">
+      <c r="OI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer398</t>
         </is>
       </c>
-      <c r="OJ1" t="inlineStr">
+      <c r="OJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer399</t>
         </is>
       </c>
-      <c r="OK1" t="inlineStr">
+      <c r="OK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer400</t>
         </is>
       </c>
-      <c r="OL1" t="inlineStr">
+      <c r="OL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer401</t>
         </is>
       </c>
-      <c r="OM1" t="inlineStr">
+      <c r="OM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer402</t>
         </is>
       </c>
-      <c r="ON1" t="inlineStr">
+      <c r="ON1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer403</t>
         </is>
       </c>
-      <c r="OO1" t="inlineStr">
+      <c r="OO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer404</t>
         </is>
       </c>
-      <c r="OP1" t="inlineStr">
+      <c r="OP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer405</t>
         </is>
       </c>
-      <c r="OQ1" t="inlineStr">
+      <c r="OQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer406</t>
         </is>
       </c>
-      <c r="OR1" t="inlineStr">
+      <c r="OR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer407</t>
         </is>
       </c>
-      <c r="OS1" t="inlineStr">
+      <c r="OS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer408</t>
         </is>
       </c>
-      <c r="OT1" t="inlineStr">
+      <c r="OT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer409</t>
         </is>
       </c>
-      <c r="OU1" t="inlineStr">
+      <c r="OU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer410</t>
         </is>
       </c>
-      <c r="OV1" t="inlineStr">
+      <c r="OV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer411</t>
         </is>
       </c>
-      <c r="OW1" t="inlineStr">
+      <c r="OW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer412</t>
         </is>
       </c>
-      <c r="OX1" t="inlineStr">
+      <c r="OX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer413</t>
         </is>
       </c>
-      <c r="OY1" t="inlineStr">
+      <c r="OY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer414</t>
         </is>
       </c>
-      <c r="OZ1" t="inlineStr">
+      <c r="OZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer415</t>
         </is>
       </c>
-      <c r="PA1" t="inlineStr">
+      <c r="PA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer416</t>
         </is>
       </c>
-      <c r="PB1" t="inlineStr">
+      <c r="PB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer417</t>
         </is>
       </c>
-      <c r="PC1" t="inlineStr">
+      <c r="PC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer418</t>
         </is>
       </c>
-      <c r="PD1" t="inlineStr">
+      <c r="PD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer419</t>
         </is>
       </c>
-      <c r="PE1" t="inlineStr">
+      <c r="PE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer420</t>
         </is>
       </c>
-      <c r="PF1" t="inlineStr">
+      <c r="PF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer421</t>
         </is>
       </c>
-      <c r="PG1" t="inlineStr">
+      <c r="PG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer422</t>
         </is>
       </c>
-      <c r="PH1" t="inlineStr">
+      <c r="PH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer423</t>
         </is>
       </c>
-      <c r="PI1" t="inlineStr">
+      <c r="PI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer424</t>
         </is>
       </c>
-      <c r="PJ1" t="inlineStr">
+      <c r="PJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer425</t>
         </is>
       </c>
-      <c r="PK1" t="inlineStr">
+      <c r="PK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer426</t>
         </is>
       </c>
-      <c r="PL1" t="inlineStr">
+      <c r="PL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer427</t>
         </is>
       </c>
-      <c r="PM1" t="inlineStr">
+      <c r="PM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer428</t>
         </is>
       </c>
-      <c r="PN1" t="inlineStr">
+      <c r="PN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer429</t>
         </is>
       </c>
-      <c r="PO1" t="inlineStr">
+      <c r="PO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer430</t>
         </is>
       </c>
-      <c r="PP1" t="inlineStr">
+      <c r="PP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer431</t>
         </is>
       </c>
-      <c r="PQ1" t="inlineStr">
+      <c r="PQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer432</t>
         </is>
       </c>
-      <c r="PR1" t="inlineStr">
+      <c r="PR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer433</t>
         </is>
       </c>
-      <c r="PS1" t="inlineStr">
+      <c r="PS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer434</t>
         </is>
       </c>
-      <c r="PT1" t="inlineStr">
+      <c r="PT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer435</t>
         </is>
       </c>
-      <c r="PU1" t="inlineStr">
+      <c r="PU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer436</t>
         </is>
       </c>
-      <c r="PV1" t="inlineStr">
+      <c r="PV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer437</t>
         </is>
       </c>
-      <c r="PW1" t="inlineStr">
+      <c r="PW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer438</t>
         </is>
       </c>
-      <c r="PX1" t="inlineStr">
+      <c r="PX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer439</t>
         </is>
       </c>
-      <c r="PY1" t="inlineStr">
+      <c r="PY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer440</t>
         </is>
       </c>
-      <c r="PZ1" t="inlineStr">
+      <c r="PZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer441</t>
         </is>
       </c>
-      <c r="QA1" t="inlineStr">
+      <c r="QA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer442</t>
         </is>
       </c>
-      <c r="QB1" t="inlineStr">
+      <c r="QB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer443</t>
         </is>
       </c>
-      <c r="QC1" t="inlineStr">
+      <c r="QC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer444</t>
         </is>
       </c>
-      <c r="QD1" t="inlineStr">
+      <c r="QD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer445</t>
         </is>
       </c>
-      <c r="QE1" t="inlineStr">
+      <c r="QE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer446</t>
         </is>
       </c>
-      <c r="QF1" t="inlineStr">
+      <c r="QF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer447</t>
         </is>
       </c>
-      <c r="QG1" t="inlineStr">
+      <c r="QG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer448</t>
         </is>
       </c>
-      <c r="QH1" t="inlineStr">
+      <c r="QH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer449</t>
         </is>
       </c>
-      <c r="QI1" t="inlineStr">
+      <c r="QI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer450</t>
         </is>
       </c>
-      <c r="QJ1" t="inlineStr">
+      <c r="QJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer451</t>
         </is>
       </c>
-      <c r="QK1" t="inlineStr">
+      <c r="QK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer452</t>
         </is>
       </c>
-      <c r="QL1" t="inlineStr">
+      <c r="QL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer453</t>
         </is>
       </c>
-      <c r="QM1" t="inlineStr">
+      <c r="QM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer454</t>
         </is>
       </c>
-      <c r="QN1" t="inlineStr">
+      <c r="QN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer455</t>
         </is>
       </c>
-      <c r="QO1" t="inlineStr">
+      <c r="QO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer456</t>
         </is>
       </c>
-      <c r="QP1" t="inlineStr">
+      <c r="QP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer457</t>
         </is>
       </c>
-      <c r="QQ1" t="inlineStr">
+      <c r="QQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer458</t>
         </is>
       </c>
-      <c r="QR1" t="inlineStr">
+      <c r="QR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer459</t>
         </is>
       </c>
-      <c r="QS1" t="inlineStr">
+      <c r="QS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer460</t>
         </is>
       </c>
-      <c r="QT1" t="inlineStr">
+      <c r="QT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer461</t>
         </is>
       </c>
-      <c r="QU1" t="inlineStr">
+      <c r="QU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer462</t>
         </is>
       </c>
-      <c r="QV1" t="inlineStr">
+      <c r="QV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer463</t>
         </is>
       </c>
-      <c r="QW1" t="inlineStr">
+      <c r="QW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer464</t>
         </is>
       </c>
-      <c r="QX1" t="inlineStr">
+      <c r="QX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer465</t>
         </is>
       </c>
-      <c r="QY1" t="inlineStr">
+      <c r="QY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer466</t>
         </is>
       </c>
-      <c r="QZ1" t="inlineStr">
+      <c r="QZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer467</t>
         </is>
       </c>
-      <c r="RA1" t="inlineStr">
+      <c r="RA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer468</t>
         </is>
       </c>
-      <c r="RB1" t="inlineStr">
+      <c r="RB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer469</t>
         </is>
       </c>
-      <c r="RC1" t="inlineStr">
+      <c r="RC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer470</t>
         </is>
       </c>
-      <c r="RD1" t="inlineStr">
+      <c r="RD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer471</t>
         </is>
       </c>
-      <c r="RE1" t="inlineStr">
+      <c r="RE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer472</t>
         </is>
       </c>
-      <c r="RF1" t="inlineStr">
+      <c r="RF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer473</t>
         </is>
       </c>
-      <c r="RG1" t="inlineStr">
+      <c r="RG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer474</t>
         </is>
       </c>
-      <c r="RH1" t="inlineStr">
+      <c r="RH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer475</t>
         </is>
       </c>
-      <c r="RI1" t="inlineStr">
+      <c r="RI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer476</t>
         </is>
       </c>
-      <c r="RJ1" t="inlineStr">
+      <c r="RJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer477</t>
         </is>
       </c>
-      <c r="RK1" t="inlineStr">
+      <c r="RK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer478</t>
         </is>
       </c>
-      <c r="RL1" t="inlineStr">
+      <c r="RL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer479</t>
         </is>
       </c>
-      <c r="RM1" t="inlineStr">
+      <c r="RM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer480</t>
         </is>
       </c>
-      <c r="RN1" t="inlineStr">
+      <c r="RN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer481</t>
         </is>
       </c>
-      <c r="RO1" t="inlineStr">
+      <c r="RO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer482</t>
         </is>
       </c>
-      <c r="RP1" t="inlineStr">
+      <c r="RP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer483</t>
         </is>
       </c>
-      <c r="RQ1" t="inlineStr">
+      <c r="RQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer484</t>
         </is>
       </c>
-      <c r="RR1" t="inlineStr">
+      <c r="RR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer485</t>
         </is>
       </c>
-      <c r="RS1" t="inlineStr">
+      <c r="RS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer486</t>
         </is>
       </c>
-      <c r="RT1" t="inlineStr">
+      <c r="RT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer487</t>
         </is>
       </c>
-      <c r="RU1" t="inlineStr">
+      <c r="RU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer488</t>
         </is>
       </c>
-      <c r="RV1" t="inlineStr">
+      <c r="RV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer489</t>
         </is>
       </c>
-      <c r="RW1" t="inlineStr">
+      <c r="RW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer490</t>
         </is>
       </c>
-      <c r="RX1" t="inlineStr">
+      <c r="RX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer491</t>
         </is>
       </c>
-      <c r="RY1" t="inlineStr">
+      <c r="RY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer492</t>
         </is>
       </c>
-      <c r="RZ1" t="inlineStr">
+      <c r="RZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer493</t>
         </is>
       </c>
-      <c r="SA1" t="inlineStr">
+      <c r="SA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer494</t>
         </is>
       </c>
-      <c r="SB1" t="inlineStr">
+      <c r="SB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer495</t>
         </is>
       </c>
-      <c r="SC1" t="inlineStr">
+      <c r="SC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer496</t>
         </is>
       </c>
-      <c r="SD1" t="inlineStr">
+      <c r="SD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer497</t>
         </is>
       </c>
-      <c r="SE1" t="inlineStr">
+      <c r="SE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer498</t>
         </is>
       </c>
-      <c r="SF1" t="inlineStr">
+      <c r="SF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer499</t>
         </is>
       </c>
-      <c r="SG1" t="inlineStr">
+      <c r="SG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer500</t>
         </is>
       </c>
-      <c r="SH1" t="inlineStr">
+      <c r="SH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer501</t>
         </is>
       </c>
-      <c r="SI1" t="inlineStr">
+      <c r="SI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer502</t>
         </is>
       </c>
-      <c r="SJ1" t="inlineStr">
+      <c r="SJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer503</t>
         </is>
       </c>
-      <c r="SK1" t="inlineStr">
+      <c r="SK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer504</t>
         </is>
       </c>
-      <c r="SL1" t="inlineStr">
+      <c r="SL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer505</t>
         </is>
       </c>
-      <c r="SM1" t="inlineStr">
+      <c r="SM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer506</t>
         </is>
       </c>
-      <c r="SN1" t="inlineStr">
+      <c r="SN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer507</t>
         </is>
       </c>
-      <c r="SO1" t="inlineStr">
+      <c r="SO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer508</t>
         </is>
       </c>
-      <c r="SP1" t="inlineStr">
+      <c r="SP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer509</t>
         </is>
       </c>
-      <c r="SQ1" t="inlineStr">
+      <c r="SQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer510</t>
         </is>
       </c>
-      <c r="SR1" t="inlineStr">
+      <c r="SR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer511</t>
         </is>
       </c>
-      <c r="SS1" t="inlineStr">
+      <c r="SS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer512</t>
         </is>
       </c>
-      <c r="ST1" t="inlineStr">
+      <c r="ST1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer513</t>
         </is>
       </c>
-      <c r="SU1" t="inlineStr">
+      <c r="SU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer514</t>
         </is>
       </c>
-      <c r="SV1" t="inlineStr">
+      <c r="SV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer515</t>
         </is>
       </c>
-      <c r="SW1" t="inlineStr">
+      <c r="SW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer516</t>
         </is>
       </c>
-      <c r="SX1" t="inlineStr">
+      <c r="SX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer517</t>
         </is>
       </c>
-      <c r="SY1" t="inlineStr">
+      <c r="SY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer518</t>
         </is>
       </c>
-      <c r="SZ1" t="inlineStr">
+      <c r="SZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer519</t>
         </is>
       </c>
-      <c r="TA1" t="inlineStr">
+      <c r="TA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer520</t>
         </is>
       </c>
-      <c r="TB1" t="inlineStr">
+      <c r="TB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer521</t>
         </is>
       </c>
-      <c r="TC1" t="inlineStr">
+      <c r="TC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer522</t>
         </is>
       </c>
-      <c r="TD1" t="inlineStr">
+      <c r="TD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer523</t>
         </is>
       </c>
-      <c r="TE1" t="inlineStr">
+      <c r="TE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer524</t>
         </is>
       </c>
-      <c r="TF1" t="inlineStr">
+      <c r="TF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer525</t>
         </is>
       </c>
-      <c r="TG1" t="inlineStr">
+      <c r="TG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer526</t>
         </is>
       </c>
-      <c r="TH1" t="inlineStr">
+      <c r="TH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer527</t>
         </is>
       </c>
-      <c r="TI1" t="inlineStr">
+      <c r="TI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer528</t>
         </is>
       </c>
-      <c r="TJ1" t="inlineStr">
+      <c r="TJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer529</t>
         </is>
       </c>
-      <c r="TK1" t="inlineStr">
+      <c r="TK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer530</t>
         </is>
       </c>
-      <c r="TL1" t="inlineStr">
+      <c r="TL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer531</t>
         </is>
       </c>
-      <c r="TM1" t="inlineStr">
+      <c r="TM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer532</t>
         </is>
       </c>
-      <c r="TN1" t="inlineStr">
+      <c r="TN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer533</t>
         </is>
       </c>
-      <c r="TO1" t="inlineStr">
+      <c r="TO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer534</t>
         </is>
       </c>
-      <c r="TP1" t="inlineStr">
+      <c r="TP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer535</t>
         </is>
       </c>
-      <c r="TQ1" t="inlineStr">
+      <c r="TQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer536</t>
         </is>
       </c>
-      <c r="TR1" t="inlineStr">
+      <c r="TR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer537</t>
         </is>
       </c>
-      <c r="TS1" t="inlineStr">
+      <c r="TS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer538</t>
         </is>
       </c>
-      <c r="TT1" t="inlineStr">
+      <c r="TT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer539</t>
         </is>
       </c>
-      <c r="TU1" t="inlineStr">
+      <c r="TU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer540</t>
         </is>
       </c>
-      <c r="TV1" t="inlineStr">
+      <c r="TV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer541</t>
         </is>
       </c>
-      <c r="TW1" t="inlineStr">
+      <c r="TW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer542</t>
         </is>
       </c>
-      <c r="TX1" t="inlineStr">
+      <c r="TX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer543</t>
         </is>
       </c>
-      <c r="TY1" t="inlineStr">
+      <c r="TY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer544</t>
         </is>
       </c>
-      <c r="TZ1" t="inlineStr">
+      <c r="TZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer545</t>
         </is>
       </c>
-      <c r="UA1" t="inlineStr">
+      <c r="UA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer546</t>
         </is>
       </c>
-      <c r="UB1" t="inlineStr">
+      <c r="UB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer547</t>
         </is>
       </c>
-      <c r="UC1" t="inlineStr">
+      <c r="UC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer548</t>
         </is>
       </c>
-      <c r="UD1" t="inlineStr">
+      <c r="UD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer549</t>
         </is>
       </c>
-      <c r="UE1" t="inlineStr">
+      <c r="UE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer550</t>
         </is>
       </c>
-      <c r="UF1" t="inlineStr">
+      <c r="UF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer551</t>
         </is>
       </c>
-      <c r="UG1" t="inlineStr">
+      <c r="UG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer552</t>
         </is>
       </c>
-      <c r="UH1" t="inlineStr">
+      <c r="UH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer553</t>
         </is>
       </c>
-      <c r="UI1" t="inlineStr">
+      <c r="UI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer554</t>
         </is>
       </c>
-      <c r="UJ1" t="inlineStr">
+      <c r="UJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer555</t>
         </is>
       </c>
-      <c r="UK1" t="inlineStr">
+      <c r="UK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer556</t>
         </is>
       </c>
-      <c r="UL1" t="inlineStr">
+      <c r="UL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer557</t>
         </is>
       </c>
-      <c r="UM1" t="inlineStr">
+      <c r="UM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer558</t>
         </is>
       </c>
-      <c r="UN1" t="inlineStr">
+      <c r="UN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer559</t>
         </is>
       </c>
-      <c r="UO1" t="inlineStr">
+      <c r="UO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer560</t>
         </is>
       </c>
-      <c r="UP1" t="inlineStr">
+      <c r="UP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer561</t>
         </is>
       </c>
-      <c r="UQ1" t="inlineStr">
+      <c r="UQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer562</t>
         </is>
       </c>
-      <c r="UR1" t="inlineStr">
+      <c r="UR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer563</t>
         </is>
       </c>
-      <c r="US1" t="inlineStr">
+      <c r="US1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer564</t>
         </is>
       </c>
-      <c r="UT1" t="inlineStr">
+      <c r="UT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer565</t>
         </is>
       </c>
-      <c r="UU1" t="inlineStr">
+      <c r="UU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer566</t>
         </is>
       </c>
-      <c r="UV1" t="inlineStr">
+      <c r="UV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer567</t>
         </is>
       </c>
-      <c r="UW1" t="inlineStr">
+      <c r="UW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer568</t>
         </is>
       </c>
-      <c r="UX1" t="inlineStr">
+      <c r="UX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer569</t>
         </is>
       </c>
-      <c r="UY1" t="inlineStr">
+      <c r="UY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer570</t>
         </is>
       </c>
-      <c r="UZ1" t="inlineStr">
+      <c r="UZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer571</t>
         </is>
       </c>
-      <c r="VA1" t="inlineStr">
+      <c r="VA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer572</t>
         </is>
       </c>
-      <c r="VB1" t="inlineStr">
+      <c r="VB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer573</t>
         </is>
       </c>
-      <c r="VC1" t="inlineStr">
+      <c r="VC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer574</t>
         </is>
       </c>
-      <c r="VD1" t="inlineStr">
+      <c r="VD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer575</t>
         </is>
       </c>
-      <c r="VE1" t="inlineStr">
+      <c r="VE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer576</t>
         </is>
       </c>
-      <c r="VF1" t="inlineStr">
+      <c r="VF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer577</t>
         </is>
       </c>
-      <c r="VG1" t="inlineStr">
+      <c r="VG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer578</t>
         </is>
       </c>
-      <c r="VH1" t="inlineStr">
+      <c r="VH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer579</t>
         </is>
       </c>
-      <c r="VI1" t="inlineStr">
+      <c r="VI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer580</t>
         </is>
       </c>
-      <c r="VJ1" t="inlineStr">
+      <c r="VJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer581</t>
         </is>
       </c>
-      <c r="VK1" t="inlineStr">
+      <c r="VK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer582</t>
         </is>
       </c>
-      <c r="VL1" t="inlineStr">
+      <c r="VL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer583</t>
         </is>
       </c>
-      <c r="VM1" t="inlineStr">
+      <c r="VM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer584</t>
         </is>
       </c>
-      <c r="VN1" t="inlineStr">
+      <c r="VN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer585</t>
         </is>
       </c>
-      <c r="VO1" t="inlineStr">
+      <c r="VO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer586</t>
         </is>
       </c>
-      <c r="VP1" t="inlineStr">
+      <c r="VP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer587</t>
         </is>
       </c>
-      <c r="VQ1" t="inlineStr">
+      <c r="VQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer588</t>
         </is>
       </c>
-      <c r="VR1" t="inlineStr">
+      <c r="VR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer589</t>
         </is>
       </c>
-      <c r="VS1" t="inlineStr">
+      <c r="VS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer590</t>
         </is>
       </c>
-      <c r="VT1" t="inlineStr">
+      <c r="VT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer591</t>
         </is>
       </c>
-      <c r="VU1" t="inlineStr">
+      <c r="VU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer592</t>
         </is>
       </c>
-      <c r="VV1" t="inlineStr">
+      <c r="VV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer593</t>
         </is>
       </c>
-      <c r="VW1" t="inlineStr">
+      <c r="VW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer594</t>
         </is>
       </c>
-      <c r="VX1" t="inlineStr">
+      <c r="VX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer595</t>
         </is>
       </c>
-      <c r="VY1" t="inlineStr">
+      <c r="VY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer596</t>
         </is>
       </c>
-      <c r="VZ1" t="inlineStr">
+      <c r="VZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer597</t>
         </is>
       </c>
-      <c r="WA1" t="inlineStr">
+      <c r="WA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer598</t>
         </is>
       </c>
-      <c r="WB1" t="inlineStr">
+      <c r="WB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer599</t>
         </is>
       </c>
-      <c r="WC1" t="inlineStr">
+      <c r="WC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer600</t>
         </is>
       </c>
-      <c r="WD1" t="inlineStr">
+      <c r="WD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer601</t>
         </is>
       </c>
-      <c r="WE1" t="inlineStr">
+      <c r="WE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer602</t>
         </is>
       </c>
-      <c r="WF1" t="inlineStr">
+      <c r="WF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer603</t>
         </is>
       </c>
-      <c r="WG1" t="inlineStr">
+      <c r="WG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer604</t>
         </is>
       </c>
-      <c r="WH1" t="inlineStr">
+      <c r="WH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer605</t>
         </is>
       </c>
-      <c r="WI1" t="inlineStr">
+      <c r="WI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer606</t>
         </is>
       </c>
-      <c r="WJ1" t="inlineStr">
+      <c r="WJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer607</t>
         </is>
       </c>
-      <c r="WK1" t="inlineStr">
+      <c r="WK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer608</t>
         </is>
       </c>
-      <c r="WL1" t="inlineStr">
+      <c r="WL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer609</t>
         </is>
       </c>
-      <c r="WM1" t="inlineStr">
+      <c r="WM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer610</t>
         </is>
       </c>
-      <c r="WN1" t="inlineStr">
+      <c r="WN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer611</t>
         </is>
       </c>
-      <c r="WO1" t="inlineStr">
+      <c r="WO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer612</t>
         </is>
       </c>
-      <c r="WP1" t="inlineStr">
+      <c r="WP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer613</t>
         </is>
       </c>
-      <c r="WQ1" t="inlineStr">
+      <c r="WQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer614</t>
         </is>
       </c>
-      <c r="WR1" t="inlineStr">
+      <c r="WR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer615</t>
         </is>
       </c>
-      <c r="WS1" t="inlineStr">
+      <c r="WS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer616</t>
         </is>
       </c>
-      <c r="WT1" t="inlineStr">
+      <c r="WT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer617</t>
         </is>
       </c>
-      <c r="WU1" t="inlineStr">
+      <c r="WU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer618</t>
         </is>
       </c>
-      <c r="WV1" t="inlineStr">
+      <c r="WV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer619</t>
         </is>
       </c>
-      <c r="WW1" t="inlineStr">
+      <c r="WW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer620</t>
         </is>
       </c>
-      <c r="WX1" t="inlineStr">
+      <c r="WX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer621</t>
         </is>
       </c>
-      <c r="WY1" t="inlineStr">
+      <c r="WY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer622</t>
         </is>
       </c>
-      <c r="WZ1" t="inlineStr">
+      <c r="WZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer623</t>
         </is>
       </c>
-      <c r="XA1" t="inlineStr">
+      <c r="XA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer624</t>
         </is>
       </c>
-      <c r="XB1" t="inlineStr">
+      <c r="XB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer625</t>
         </is>
       </c>
-      <c r="XC1" t="inlineStr">
+      <c r="XC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer626</t>
         </is>
       </c>
-      <c r="XD1" t="inlineStr">
+      <c r="XD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer627</t>
         </is>
       </c>
-      <c r="XE1" t="inlineStr">
+      <c r="XE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer628</t>
         </is>
       </c>
-      <c r="XF1" t="inlineStr">
+      <c r="XF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer629</t>
         </is>
       </c>
-      <c r="XG1" t="inlineStr">
+      <c r="XG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer630</t>
         </is>
       </c>
-      <c r="XH1" t="inlineStr">
+      <c r="XH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer631</t>
         </is>
       </c>
-      <c r="XI1" t="inlineStr">
+      <c r="XI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer632</t>
         </is>
       </c>
-      <c r="XJ1" t="inlineStr">
+      <c r="XJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer633</t>
         </is>
       </c>
-      <c r="XK1" t="inlineStr">
+      <c r="XK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer634</t>
         </is>
       </c>
-      <c r="XL1" t="inlineStr">
+      <c r="XL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer635</t>
         </is>
       </c>
-      <c r="XM1" t="inlineStr">
+      <c r="XM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer636</t>
         </is>
       </c>
-      <c r="XN1" t="inlineStr">
+      <c r="XN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer637</t>
         </is>
       </c>
-      <c r="XO1" t="inlineStr">
+      <c r="XO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer638</t>
         </is>
       </c>
-      <c r="XP1" t="inlineStr">
+      <c r="XP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer639</t>
         </is>
       </c>
-      <c r="XQ1" t="inlineStr">
+      <c r="XQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer640</t>
         </is>
       </c>
-      <c r="XR1" t="inlineStr">
+      <c r="XR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer641</t>
         </is>
       </c>
-      <c r="XS1" t="inlineStr">
+      <c r="XS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer642</t>
         </is>
       </c>
-      <c r="XT1" t="inlineStr">
+      <c r="XT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer643</t>
         </is>
       </c>
-      <c r="XU1" t="inlineStr">
+      <c r="XU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer644</t>
         </is>
       </c>
-      <c r="XV1" t="inlineStr">
+      <c r="XV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer645</t>
         </is>
       </c>
-      <c r="XW1" t="inlineStr">
+      <c r="XW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer646</t>
         </is>
       </c>
-      <c r="XX1" t="inlineStr">
+      <c r="XX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer647</t>
         </is>
       </c>
-      <c r="XY1" t="inlineStr">
+      <c r="XY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer648</t>
         </is>
       </c>
-      <c r="XZ1" t="inlineStr">
+      <c r="XZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer649</t>
         </is>
       </c>
-      <c r="YA1" t="inlineStr">
+      <c r="YA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer650</t>
         </is>
       </c>
-      <c r="YB1" t="inlineStr">
+      <c r="YB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer651</t>
         </is>
       </c>
-      <c r="YC1" t="inlineStr">
+      <c r="YC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer652</t>
         </is>
       </c>
-      <c r="YD1" t="inlineStr">
+      <c r="YD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer653</t>
         </is>
       </c>
-      <c r="YE1" t="inlineStr">
+      <c r="YE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer654</t>
         </is>
       </c>
-      <c r="YF1" t="inlineStr">
+      <c r="YF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer655</t>
         </is>
       </c>
-      <c r="YG1" t="inlineStr">
+      <c r="YG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer656</t>
         </is>
       </c>
-      <c r="YH1" t="inlineStr">
+      <c r="YH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer657</t>
         </is>
       </c>
-      <c r="YI1" t="inlineStr">
+      <c r="YI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer658</t>
         </is>
       </c>
-      <c r="YJ1" t="inlineStr">
+      <c r="YJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer659</t>
         </is>
       </c>
-      <c r="YK1" t="inlineStr">
+      <c r="YK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer660</t>
         </is>
       </c>
-      <c r="YL1" t="inlineStr">
+      <c r="YL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer661</t>
         </is>
       </c>
-      <c r="YM1" t="inlineStr">
+      <c r="YM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer662</t>
         </is>
       </c>
-      <c r="YN1" t="inlineStr">
+      <c r="YN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer663</t>
         </is>
       </c>
-      <c r="YO1" t="inlineStr">
+      <c r="YO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer664</t>
         </is>
       </c>
-      <c r="YP1" t="inlineStr">
+      <c r="YP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer665</t>
         </is>
       </c>
-      <c r="YQ1" t="inlineStr">
+      <c r="YQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer666</t>
         </is>
       </c>
-      <c r="YR1" t="inlineStr">
+      <c r="YR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer667</t>
         </is>
       </c>
-      <c r="YS1" t="inlineStr">
+      <c r="YS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer668</t>
         </is>
       </c>
-      <c r="YT1" t="inlineStr">
+      <c r="YT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer669</t>
         </is>
       </c>
-      <c r="YU1" t="inlineStr">
+      <c r="YU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer670</t>
         </is>
       </c>
-      <c r="YV1" t="inlineStr">
+      <c r="YV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer671</t>
         </is>
       </c>
-      <c r="YW1" t="inlineStr">
+      <c r="YW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer672</t>
         </is>
       </c>
-      <c r="YX1" t="inlineStr">
+      <c r="YX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer673</t>
         </is>
       </c>
-      <c r="YY1" t="inlineStr">
+      <c r="YY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer674</t>
         </is>
       </c>
-      <c r="YZ1" t="inlineStr">
+      <c r="YZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer675</t>
         </is>
       </c>
-      <c r="ZA1" t="inlineStr">
+      <c r="ZA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer676</t>
         </is>
       </c>
-      <c r="ZB1" t="inlineStr">
+      <c r="ZB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer677</t>
         </is>
       </c>
-      <c r="ZC1" t="inlineStr">
+      <c r="ZC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer678</t>
         </is>
       </c>
-      <c r="ZD1" t="inlineStr">
+      <c r="ZD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer679</t>
         </is>
       </c>
-      <c r="ZE1" t="inlineStr">
+      <c r="ZE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer680</t>
         </is>
       </c>
-      <c r="ZF1" t="inlineStr">
+      <c r="ZF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer681</t>
         </is>
       </c>
-      <c r="ZG1" t="inlineStr">
+      <c r="ZG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer682</t>
         </is>
       </c>
-      <c r="ZH1" t="inlineStr">
+      <c r="ZH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer683</t>
         </is>
       </c>
-      <c r="ZI1" t="inlineStr">
+      <c r="ZI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer684</t>
         </is>
       </c>
-      <c r="ZJ1" t="inlineStr">
+      <c r="ZJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer685</t>
         </is>
       </c>
-      <c r="ZK1" t="inlineStr">
+      <c r="ZK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer686</t>
         </is>
       </c>
-      <c r="ZL1" t="inlineStr">
+      <c r="ZL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer687</t>
         </is>
       </c>
-      <c r="ZM1" t="inlineStr">
+      <c r="ZM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer688</t>
         </is>
       </c>
-      <c r="ZN1" t="inlineStr">
+      <c r="ZN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer689</t>
         </is>
       </c>
-      <c r="ZO1" t="inlineStr">
+      <c r="ZO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer690</t>
         </is>
       </c>
-      <c r="ZP1" t="inlineStr">
+      <c r="ZP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer691</t>
         </is>
       </c>
-      <c r="ZQ1" t="inlineStr">
+      <c r="ZQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer692</t>
         </is>
       </c>
-      <c r="ZR1" t="inlineStr">
+      <c r="ZR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer693</t>
         </is>
       </c>
-      <c r="ZS1" t="inlineStr">
+      <c r="ZS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer694</t>
         </is>
       </c>
-      <c r="ZT1" t="inlineStr">
+      <c r="ZT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer695</t>
         </is>
       </c>
-      <c r="ZU1" t="inlineStr">
+      <c r="ZU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer696</t>
         </is>
       </c>
-      <c r="ZV1" t="inlineStr">
+      <c r="ZV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer697</t>
         </is>
       </c>
-      <c r="ZW1" t="inlineStr">
+      <c r="ZW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer698</t>
         </is>
       </c>
-      <c r="ZX1" t="inlineStr">
+      <c r="ZX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer699</t>
         </is>
       </c>
-      <c r="ZY1" t="inlineStr">
+      <c r="ZY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer700</t>
         </is>
       </c>
-      <c r="ZZ1" t="inlineStr">
+      <c r="ZZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer701</t>
         </is>
       </c>
-      <c r="AAA1" t="inlineStr">
+      <c r="AAA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer702</t>
         </is>
       </c>
-      <c r="AAB1" t="inlineStr">
+      <c r="AAB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer703</t>
         </is>
       </c>
-      <c r="AAC1" t="inlineStr">
+      <c r="AAC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer704</t>
         </is>
       </c>
-      <c r="AAD1" t="inlineStr">
+      <c r="AAD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer705</t>
         </is>
       </c>
-      <c r="AAE1" t="inlineStr">
+      <c r="AAE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer706</t>
         </is>
       </c>
-      <c r="AAF1" t="inlineStr">
+      <c r="AAF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer707</t>
         </is>
       </c>
-      <c r="AAG1" t="inlineStr">
+      <c r="AAG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer708</t>
         </is>
       </c>
-      <c r="AAH1" t="inlineStr">
+      <c r="AAH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer709</t>
         </is>
       </c>
-      <c r="AAI1" t="inlineStr">
+      <c r="AAI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer710</t>
         </is>
       </c>
-      <c r="AAJ1" t="inlineStr">
+      <c r="AAJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer711</t>
         </is>
       </c>
-      <c r="AAK1" t="inlineStr">
+      <c r="AAK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer712</t>
         </is>
       </c>
-      <c r="AAL1" t="inlineStr">
+      <c r="AAL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer713</t>
         </is>
       </c>
-      <c r="AAM1" t="inlineStr">
+      <c r="AAM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer714</t>
         </is>
       </c>
-      <c r="AAN1" t="inlineStr">
+      <c r="AAN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer715</t>
         </is>
       </c>
-      <c r="AAO1" t="inlineStr">
+      <c r="AAO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer716</t>
         </is>
       </c>
-      <c r="AAP1" t="inlineStr">
+      <c r="AAP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer717</t>
         </is>
       </c>
-      <c r="AAQ1" t="inlineStr">
+      <c r="AAQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer718</t>
         </is>
       </c>
-      <c r="AAR1" t="inlineStr">
+      <c r="AAR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer719</t>
         </is>
       </c>
-      <c r="AAS1" t="inlineStr">
+      <c r="AAS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer720</t>
         </is>
       </c>
-      <c r="AAT1" t="inlineStr">
+      <c r="AAT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer721</t>
         </is>
       </c>
-      <c r="AAU1" t="inlineStr">
+      <c r="AAU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer722</t>
         </is>
       </c>
-      <c r="AAV1" t="inlineStr">
+      <c r="AAV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer723</t>
         </is>
       </c>
-      <c r="AAW1" t="inlineStr">
+      <c r="AAW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer724</t>
         </is>
       </c>
-      <c r="AAX1" t="inlineStr">
+      <c r="AAX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer725</t>
         </is>
       </c>
-      <c r="AAY1" t="inlineStr">
+      <c r="AAY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer726</t>
         </is>
       </c>
-      <c r="AAZ1" t="inlineStr">
+      <c r="AAZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer727</t>
         </is>
       </c>
-      <c r="ABA1" t="inlineStr">
+      <c r="ABA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer728</t>
         </is>
       </c>
-      <c r="ABB1" t="inlineStr">
+      <c r="ABB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer729</t>
         </is>
       </c>
-      <c r="ABC1" t="inlineStr">
+      <c r="ABC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer730</t>
         </is>
       </c>
-      <c r="ABD1" t="inlineStr">
+      <c r="ABD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer731</t>
         </is>
       </c>
-      <c r="ABE1" t="inlineStr">
+      <c r="ABE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer732</t>
         </is>
       </c>
-      <c r="ABF1" t="inlineStr">
+      <c r="ABF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer733</t>
         </is>
       </c>
-      <c r="ABG1" t="inlineStr">
+      <c r="ABG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer734</t>
         </is>
       </c>
-      <c r="ABH1" t="inlineStr">
+      <c r="ABH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer735</t>
         </is>
       </c>
-      <c r="ABI1" t="inlineStr">
+      <c r="ABI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer736</t>
         </is>
       </c>
-      <c r="ABJ1" t="inlineStr">
+      <c r="ABJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer737</t>
         </is>
       </c>
-      <c r="ABK1" t="inlineStr">
+      <c r="ABK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer738</t>
         </is>
       </c>
-      <c r="ABL1" t="inlineStr">
+      <c r="ABL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer739</t>
         </is>
       </c>
-      <c r="ABM1" t="inlineStr">
+      <c r="ABM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer740</t>
         </is>
       </c>
-      <c r="ABN1" t="inlineStr">
+      <c r="ABN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer741</t>
         </is>
       </c>
-      <c r="ABO1" t="inlineStr">
+      <c r="ABO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer742</t>
         </is>
       </c>
-      <c r="ABP1" t="inlineStr">
+      <c r="ABP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer743</t>
         </is>
       </c>
-      <c r="ABQ1" t="inlineStr">
+      <c r="ABQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer744</t>
         </is>
       </c>
-      <c r="ABR1" t="inlineStr">
+      <c r="ABR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer745</t>
         </is>
       </c>
-      <c r="ABS1" t="inlineStr">
+      <c r="ABS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer746</t>
         </is>
       </c>
-      <c r="ABT1" t="inlineStr">
+      <c r="ABT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer747</t>
         </is>
       </c>
-      <c r="ABU1" t="inlineStr">
+      <c r="ABU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer748</t>
         </is>
       </c>
-      <c r="ABV1" t="inlineStr">
+      <c r="ABV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer749</t>
         </is>
       </c>
-      <c r="ABW1" t="inlineStr">
+      <c r="ABW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer750</t>
         </is>
       </c>
-      <c r="ABX1" t="inlineStr">
+      <c r="ABX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer751</t>
         </is>
       </c>
-      <c r="ABY1" t="inlineStr">
+      <c r="ABY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer752</t>
         </is>
       </c>
-      <c r="ABZ1" t="inlineStr">
+      <c r="ABZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer753</t>
         </is>
       </c>
-      <c r="ACA1" t="inlineStr">
+      <c r="ACA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer754</t>
         </is>
       </c>
-      <c r="ACB1" t="inlineStr">
+      <c r="ACB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer755</t>
         </is>
       </c>
-      <c r="ACC1" t="inlineStr">
+      <c r="ACC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer756</t>
         </is>
       </c>
-      <c r="ACD1" t="inlineStr">
+      <c r="ACD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer757</t>
         </is>
       </c>
-      <c r="ACE1" t="inlineStr">
+      <c r="ACE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer758</t>
         </is>
       </c>
-      <c r="ACF1" t="inlineStr">
+      <c r="ACF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer759</t>
         </is>
       </c>
-      <c r="ACG1" t="inlineStr">
+      <c r="ACG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer760</t>
         </is>
       </c>
-      <c r="ACH1" t="inlineStr">
+      <c r="ACH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer761</t>
         </is>
       </c>
-      <c r="ACI1" t="inlineStr">
+      <c r="ACI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer762</t>
         </is>
       </c>
-      <c r="ACJ1" t="inlineStr">
+      <c r="ACJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer763</t>
         </is>
       </c>
-      <c r="ACK1" t="inlineStr">
+      <c r="ACK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer764</t>
         </is>
       </c>
-      <c r="ACL1" t="inlineStr">
+      <c r="ACL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer765</t>
         </is>
       </c>
-      <c r="ACM1" t="inlineStr">
+      <c r="ACM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer766</t>
         </is>
       </c>
-      <c r="ACN1" t="inlineStr">
+      <c r="ACN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer767</t>
         </is>
       </c>
-      <c r="ACO1" t="inlineStr">
+      <c r="ACO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer768</t>
         </is>
       </c>
-      <c r="ACP1" t="inlineStr">
+      <c r="ACP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer769</t>
         </is>
       </c>
-      <c r="ACQ1" t="inlineStr">
+      <c r="ACQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer770</t>
         </is>
       </c>
-      <c r="ACR1" t="inlineStr">
+      <c r="ACR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer771</t>
         </is>
       </c>
-      <c r="ACS1" t="inlineStr">
+      <c r="ACS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer772</t>
         </is>
       </c>
-      <c r="ACT1" t="inlineStr">
+      <c r="ACT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer773</t>
         </is>
       </c>
-      <c r="ACU1" t="inlineStr">
+      <c r="ACU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer774</t>
         </is>
       </c>
-      <c r="ACV1" t="inlineStr">
+      <c r="ACV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer775</t>
         </is>
       </c>
-      <c r="ACW1" t="inlineStr">
+      <c r="ACW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer776</t>
         </is>
       </c>
-      <c r="ACX1" t="inlineStr">
+      <c r="ACX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer777</t>
         </is>
       </c>
-      <c r="ACY1" t="inlineStr">
+      <c r="ACY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer778</t>
         </is>
       </c>
-      <c r="ACZ1" t="inlineStr">
+      <c r="ACZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer779</t>
         </is>
       </c>
-      <c r="ADA1" t="inlineStr">
+      <c r="ADA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer780</t>
         </is>
       </c>
-      <c r="ADB1" t="inlineStr">
+      <c r="ADB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer781</t>
         </is>
       </c>
-      <c r="ADC1" t="inlineStr">
+      <c r="ADC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer782</t>
         </is>
       </c>
-      <c r="ADD1" t="inlineStr">
+      <c r="ADD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer783</t>
         </is>
       </c>
-      <c r="ADE1" t="inlineStr">
+      <c r="ADE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer784</t>
         </is>
       </c>
-      <c r="ADF1" t="inlineStr">
+      <c r="ADF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer785</t>
         </is>
       </c>
-      <c r="ADG1" t="inlineStr">
+      <c r="ADG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer786</t>
         </is>
       </c>
-      <c r="ADH1" t="inlineStr">
+      <c r="ADH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer787</t>
         </is>
       </c>
-      <c r="ADI1" t="inlineStr">
+      <c r="ADI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer788</t>
         </is>
       </c>
-      <c r="ADJ1" t="inlineStr">
+      <c r="ADJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer789</t>
         </is>
       </c>
-      <c r="ADK1" t="inlineStr">
+      <c r="ADK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer790</t>
         </is>
       </c>
-      <c r="ADL1" t="inlineStr">
+      <c r="ADL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer791</t>
         </is>
       </c>
-      <c r="ADM1" t="inlineStr">
+      <c r="ADM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer792</t>
         </is>
       </c>
-      <c r="ADN1" t="inlineStr">
+      <c r="ADN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer793</t>
         </is>
       </c>
-      <c r="ADO1" t="inlineStr">
+      <c r="ADO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer794</t>
         </is>
       </c>
-      <c r="ADP1" t="inlineStr">
+      <c r="ADP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer795</t>
         </is>
       </c>
-      <c r="ADQ1" t="inlineStr">
+      <c r="ADQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer796</t>
         </is>
       </c>
-      <c r="ADR1" t="inlineStr">
+      <c r="ADR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer797</t>
         </is>
       </c>
-      <c r="ADS1" t="inlineStr">
+      <c r="ADS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer798</t>
         </is>
       </c>
-      <c r="ADT1" t="inlineStr">
+      <c r="ADT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer799</t>
         </is>
       </c>
-      <c r="ADU1" t="inlineStr">
+      <c r="ADU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer800</t>
         </is>
       </c>
-      <c r="ADV1" t="inlineStr">
+      <c r="ADV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer801</t>
         </is>
       </c>
-      <c r="ADW1" t="inlineStr">
+      <c r="ADW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer802</t>
         </is>
       </c>
-      <c r="ADX1" t="inlineStr">
+      <c r="ADX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer803</t>
         </is>
       </c>
-      <c r="ADY1" t="inlineStr">
+      <c r="ADY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer804</t>
         </is>
       </c>
-      <c r="ADZ1" t="inlineStr">
+      <c r="ADZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer805</t>
         </is>
       </c>
-      <c r="AEA1" t="inlineStr">
+      <c r="AEA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer806</t>
         </is>
       </c>
-      <c r="AEB1" t="inlineStr">
+      <c r="AEB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer807</t>
         </is>
       </c>
-      <c r="AEC1" t="inlineStr">
+      <c r="AEC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer808</t>
         </is>
       </c>
-      <c r="AED1" t="inlineStr">
+      <c r="AED1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer809</t>
         </is>
       </c>
-      <c r="AEE1" t="inlineStr">
+      <c r="AEE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer810</t>
         </is>
       </c>
-      <c r="AEF1" t="inlineStr">
+      <c r="AEF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer811</t>
         </is>
       </c>
-      <c r="AEG1" t="inlineStr">
+      <c r="AEG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer812</t>
         </is>
       </c>
-      <c r="AEH1" t="inlineStr">
+      <c r="AEH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer813</t>
         </is>
       </c>
-      <c r="AEI1" t="inlineStr">
+      <c r="AEI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer814</t>
         </is>
       </c>
-      <c r="AEJ1" t="inlineStr">
+      <c r="AEJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer815</t>
         </is>
       </c>
-      <c r="AEK1" t="inlineStr">
+      <c r="AEK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer816</t>
         </is>
       </c>
-      <c r="AEL1" t="inlineStr">
+      <c r="AEL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer817</t>
         </is>
       </c>
-      <c r="AEM1" t="inlineStr">
+      <c r="AEM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer818</t>
         </is>
       </c>
-      <c r="AEN1" t="inlineStr">
+      <c r="AEN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer819</t>
         </is>
       </c>
-      <c r="AEO1" t="inlineStr">
+      <c r="AEO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer820</t>
         </is>
       </c>
-      <c r="AEP1" t="inlineStr">
+      <c r="AEP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer821</t>
         </is>
       </c>
-      <c r="AEQ1" t="inlineStr">
+      <c r="AEQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer822</t>
         </is>
       </c>
-      <c r="AER1" t="inlineStr">
+      <c r="AER1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer823</t>
         </is>
       </c>
-      <c r="AES1" t="inlineStr">
+      <c r="AES1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer824</t>
         </is>
       </c>
-      <c r="AET1" t="inlineStr">
+      <c r="AET1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer825</t>
         </is>
       </c>
-      <c r="AEU1" t="inlineStr">
+      <c r="AEU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer826</t>
         </is>
       </c>
-      <c r="AEV1" t="inlineStr">
+      <c r="AEV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer827</t>
         </is>
       </c>
-      <c r="AEW1" t="inlineStr">
+      <c r="AEW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer828</t>
         </is>
       </c>
-      <c r="AEX1" t="inlineStr">
+      <c r="AEX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer829</t>
         </is>
       </c>
-      <c r="AEY1" t="inlineStr">
+      <c r="AEY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer830</t>
         </is>
       </c>
-      <c r="AEZ1" t="inlineStr">
+      <c r="AEZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer831</t>
         </is>
       </c>
-      <c r="AFA1" t="inlineStr">
+      <c r="AFA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer832</t>
         </is>
       </c>
-      <c r="AFB1" t="inlineStr">
+      <c r="AFB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer833</t>
         </is>
       </c>
-      <c r="AFC1" t="inlineStr">
+      <c r="AFC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer834</t>
         </is>
       </c>
-      <c r="AFD1" t="inlineStr">
+      <c r="AFD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer835</t>
         </is>
       </c>
-      <c r="AFE1" t="inlineStr">
+      <c r="AFE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer836</t>
         </is>
       </c>
-      <c r="AFF1" t="inlineStr">
+      <c r="AFF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer837</t>
         </is>
       </c>
-      <c r="AFG1" t="inlineStr">
+      <c r="AFG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer838</t>
         </is>
       </c>
-      <c r="AFH1" t="inlineStr">
+      <c r="AFH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer839</t>
         </is>
       </c>
-      <c r="AFI1" t="inlineStr">
+      <c r="AFI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer840</t>
         </is>
       </c>
-      <c r="AFJ1" t="inlineStr">
+      <c r="AFJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer841</t>
         </is>
       </c>
-      <c r="AFK1" t="inlineStr">
+      <c r="AFK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer842</t>
         </is>
       </c>
-      <c r="AFL1" t="inlineStr">
+      <c r="AFL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer843</t>
         </is>
       </c>
-      <c r="AFM1" t="inlineStr">
+      <c r="AFM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer844</t>
         </is>
       </c>
-      <c r="AFN1" t="inlineStr">
+      <c r="AFN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer845</t>
         </is>
       </c>
-      <c r="AFO1" t="inlineStr">
+      <c r="AFO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer846</t>
         </is>
       </c>
-      <c r="AFP1" t="inlineStr">
+      <c r="AFP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer847</t>
         </is>
       </c>
-      <c r="AFQ1" t="inlineStr">
+      <c r="AFQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer848</t>
         </is>
       </c>
-      <c r="AFR1" t="inlineStr">
+      <c r="AFR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer849</t>
         </is>
       </c>
-      <c r="AFS1" t="inlineStr">
+      <c r="AFS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer850</t>
         </is>
       </c>
-      <c r="AFT1" t="inlineStr">
+      <c r="AFT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer851</t>
         </is>
       </c>
-      <c r="AFU1" t="inlineStr">
+      <c r="AFU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer852</t>
         </is>
       </c>
-      <c r="AFV1" t="inlineStr">
+      <c r="AFV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer853</t>
         </is>
       </c>
-      <c r="AFW1" t="inlineStr">
+      <c r="AFW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer854</t>
         </is>
       </c>
-      <c r="AFX1" t="inlineStr">
+      <c r="AFX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer855</t>
         </is>
       </c>
-      <c r="AFY1" t="inlineStr">
+      <c r="AFY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer856</t>
         </is>
       </c>
-      <c r="AFZ1" t="inlineStr">
+      <c r="AFZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer857</t>
         </is>
       </c>
-      <c r="AGA1" t="inlineStr">
+      <c r="AGA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer858</t>
         </is>
       </c>
-      <c r="AGB1" t="inlineStr">
+      <c r="AGB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer859</t>
         </is>
       </c>
-      <c r="AGC1" t="inlineStr">
+      <c r="AGC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer860</t>
         </is>
       </c>
-      <c r="AGD1" t="inlineStr">
+      <c r="AGD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer861</t>
         </is>
       </c>
-      <c r="AGE1" t="inlineStr">
+      <c r="AGE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer862</t>
         </is>
       </c>
-      <c r="AGF1" t="inlineStr">
+      <c r="AGF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer863</t>
         </is>
       </c>
-      <c r="AGG1" t="inlineStr">
+      <c r="AGG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer864</t>
         </is>
       </c>
-      <c r="AGH1" t="inlineStr">
+      <c r="AGH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer865</t>
         </is>
       </c>
-      <c r="AGI1" t="inlineStr">
+      <c r="AGI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer866</t>
         </is>
       </c>
-      <c r="AGJ1" t="inlineStr">
+      <c r="AGJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer867</t>
         </is>
       </c>
-      <c r="AGK1" t="inlineStr">
+      <c r="AGK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer868</t>
         </is>
       </c>
-      <c r="AGL1" t="inlineStr">
+      <c r="AGL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer869</t>
         </is>
       </c>
-      <c r="AGM1" t="inlineStr">
+      <c r="AGM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer870</t>
         </is>
       </c>
-      <c r="AGN1" t="inlineStr">
+      <c r="AGN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer871</t>
         </is>
       </c>
-      <c r="AGO1" t="inlineStr">
+      <c r="AGO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer872</t>
         </is>
       </c>
-      <c r="AGP1" t="inlineStr">
+      <c r="AGP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer873</t>
         </is>
       </c>
-      <c r="AGQ1" t="inlineStr">
+      <c r="AGQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer874</t>
         </is>
       </c>
-      <c r="AGR1" t="inlineStr">
+      <c r="AGR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer875</t>
         </is>
       </c>
-      <c r="AGS1" t="inlineStr">
+      <c r="AGS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer876</t>
         </is>
       </c>
-      <c r="AGT1" t="inlineStr">
+      <c r="AGT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer877</t>
         </is>
       </c>
-      <c r="AGU1" t="inlineStr">
+      <c r="AGU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer878</t>
         </is>
       </c>
-      <c r="AGV1" t="inlineStr">
+      <c r="AGV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer879</t>
         </is>
       </c>
-      <c r="AGW1" t="inlineStr">
+      <c r="AGW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer880</t>
         </is>
       </c>
-      <c r="AGX1" t="inlineStr">
+      <c r="AGX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer881</t>
         </is>
       </c>
-      <c r="AGY1" t="inlineStr">
+      <c r="AGY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer882</t>
         </is>
       </c>
-      <c r="AGZ1" t="inlineStr">
+      <c r="AGZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer883</t>
         </is>
       </c>
-      <c r="AHA1" t="inlineStr">
+      <c r="AHA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer884</t>
         </is>
       </c>
-      <c r="AHB1" t="inlineStr">
+      <c r="AHB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer885</t>
         </is>
       </c>
-      <c r="AHC1" t="inlineStr">
+      <c r="AHC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer886</t>
         </is>
       </c>
-      <c r="AHD1" t="inlineStr">
+      <c r="AHD1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer887</t>
         </is>
       </c>
-      <c r="AHE1" t="inlineStr">
+      <c r="AHE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer888</t>
         </is>
       </c>
-      <c r="AHF1" t="inlineStr">
+      <c r="AHF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer889</t>
         </is>
       </c>
-      <c r="AHG1" t="inlineStr">
+      <c r="AHG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer890</t>
         </is>
       </c>
-      <c r="AHH1" t="inlineStr">
+      <c r="AHH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer891</t>
         </is>
       </c>
-      <c r="AHI1" t="inlineStr">
+      <c r="AHI1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer892</t>
         </is>
       </c>
-      <c r="AHJ1" t="inlineStr">
+      <c r="AHJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer893</t>
         </is>
       </c>
-      <c r="AHK1" t="inlineStr">
+      <c r="AHK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer894</t>
         </is>
       </c>
-      <c r="AHL1" t="inlineStr">
+      <c r="AHL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer895</t>
         </is>
       </c>
-      <c r="AHM1" t="inlineStr">
+      <c r="AHM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer896</t>
         </is>
       </c>
-      <c r="AHN1" t="inlineStr">
+      <c r="AHN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer897</t>
         </is>
       </c>
-      <c r="AHO1" t="inlineStr">
+      <c r="AHO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer898</t>
         </is>
       </c>
-      <c r="AHP1" t="inlineStr">
+      <c r="AHP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer899</t>
         </is>
       </c>
-      <c r="AHQ1" t="inlineStr">
+      <c r="AHQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer900</t>
         </is>
       </c>
-      <c r="AHR1" t="inlineStr">
+      <c r="AHR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer901</t>
         </is>
       </c>
-      <c r="AHS1" t="inlineStr">
+      <c r="AHS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer902</t>
         </is>
       </c>
-      <c r="AHT1" t="inlineStr">
+      <c r="AHT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer903</t>
         </is>
       </c>
-      <c r="AHU1" t="inlineStr">
+      <c r="AHU1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer904</t>
         </is>
       </c>
-      <c r="AHV1" t="inlineStr">
+      <c r="AHV1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer905</t>
         </is>
       </c>
-      <c r="AHW1" t="inlineStr">
+      <c r="AHW1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer906</t>
         </is>
       </c>
-      <c r="AHX1" t="inlineStr">
+      <c r="AHX1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer907</t>
         </is>
       </c>
-      <c r="AHY1" t="inlineStr">
+      <c r="AHY1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer908</t>
         </is>
       </c>
-      <c r="AHZ1" t="inlineStr">
+      <c r="AHZ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer909</t>
         </is>
       </c>
-      <c r="AIA1" t="inlineStr">
+      <c r="AIA1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer910</t>
         </is>
       </c>
-      <c r="AIB1" t="inlineStr">
+      <c r="AIB1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer911</t>
         </is>
       </c>
-      <c r="AIC1" t="inlineStr">
+      <c r="AIC1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer912</t>
         </is>
       </c>
-      <c r="AID1" t="inlineStr">
+      <c r="AID1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer913</t>
         </is>
       </c>
-      <c r="AIE1" t="inlineStr">
+      <c r="AIE1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer914</t>
         </is>
       </c>
-      <c r="AIF1" t="inlineStr">
+      <c r="AIF1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer915</t>
         </is>
       </c>
-      <c r="AIG1" t="inlineStr">
+      <c r="AIG1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer916</t>
         </is>
       </c>
-      <c r="AIH1" t="inlineStr">
+      <c r="AIH1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer917</t>
         </is>
       </c>
-      <c r="AII1" t="inlineStr">
+      <c r="AII1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer918</t>
         </is>
       </c>
-      <c r="AIJ1" t="inlineStr">
+      <c r="AIJ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer919</t>
         </is>
       </c>
-      <c r="AIK1" t="inlineStr">
+      <c r="AIK1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer920</t>
         </is>
       </c>
-      <c r="AIL1" t="inlineStr">
+      <c r="AIL1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer921</t>
         </is>
       </c>
-      <c r="AIM1" t="inlineStr">
+      <c r="AIM1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer922</t>
         </is>
       </c>
-      <c r="AIN1" t="inlineStr">
+      <c r="AIN1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer923</t>
         </is>
       </c>
-      <c r="AIO1" t="inlineStr">
+      <c r="AIO1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer924</t>
         </is>
       </c>
-      <c r="AIP1" t="inlineStr">
+      <c r="AIP1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer925</t>
         </is>
       </c>
-      <c r="AIQ1" t="inlineStr">
+      <c r="AIQ1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer926</t>
         </is>
       </c>
-      <c r="AIR1" t="inlineStr">
+      <c r="AIR1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer927</t>
         </is>
       </c>
-      <c r="AIS1" t="inlineStr">
+      <c r="AIS1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer928</t>
         </is>
       </c>
-      <c r="AIT1" t="inlineStr">
+      <c r="AIT1" s="1" t="inlineStr">
         <is>
           <t>ContractOffer929</t>
         </is>
@@ -5086,1562 +5098,1562 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>00100001000100100000000010010011</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000000100</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000000101</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000000110</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000000111</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010011110</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010011010</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000001010</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000001011</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000001100</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000001101</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000001110</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000001111</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010000</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010001</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010010</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001101</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010100</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010101</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010110</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010111</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011000</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011001</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010010100</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010011101</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011100</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011101</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001110</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011111</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100000</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100001</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100010</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100011</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001000</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100101</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100110</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100111</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101000</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101001</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101010</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101011</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101100</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101101</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010011000</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101111</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000110000</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001010</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010010010</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000110011</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010010000</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010010101</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000110110</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000101</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111000</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111001</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111010</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111011</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111100</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111101</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111110</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111111</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010011111</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001100</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000010</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001011</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000100</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010010111</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000110</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000111</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001000</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001001</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001010</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010100001</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001100</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001101</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001110</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001111</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010000</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100000110</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010010</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001111</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010100</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010101</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111110</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100000111</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111100</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011001</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000001</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011011</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011100</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011101</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010011011</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010011100</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100000</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100001</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000000</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100011</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100100</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100101</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100110</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100111</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101000</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101001</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010010001</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010010110</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101100</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111011</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101110</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101111</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110000</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110001</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110010</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110011</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110100</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110101</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110110</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001001</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111000</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111001</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111010</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
           <t>00100001000100100000000000000011</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000000100</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000000101</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000000110</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000000111</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>00100001000100100000000000001000</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>00100001000100100000000000001001</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000001010</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000001011</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000001100</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000001101</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000001110</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000001111</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000010000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000010001</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000010010</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100001101</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011010</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011011</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011110</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100010011</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101110</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100011000</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100100111</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000110100</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100001100</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100010010</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111101</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000000</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000001</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000011</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000101</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001011</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010001</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010011</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010110</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100001011</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011000</t>
+        </is>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011010</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011110</t>
+        </is>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011111</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100010</t>
+        </is>
+      </c>
+      <c r="EW2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101010</t>
+        </is>
+      </c>
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101011</t>
+        </is>
+      </c>
+      <c r="EY2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100011011</t>
+        </is>
+      </c>
+      <c r="EZ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100001000</t>
+        </is>
+      </c>
+      <c r="FA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111111</t>
+        </is>
+      </c>
+      <c r="FB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000010</t>
+        </is>
+      </c>
+      <c r="FC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000011</t>
+        </is>
+      </c>
+      <c r="FD2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000100</t>
+        </is>
+      </c>
+      <c r="FE2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000110</t>
+        </is>
+      </c>
+      <c r="FF2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000111</t>
+        </is>
+      </c>
+      <c r="FG2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010011001</t>
+        </is>
+      </c>
+      <c r="FH2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100101010</t>
+        </is>
+      </c>
+      <c r="FI2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010100010</t>
+        </is>
+      </c>
+      <c r="FJ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010100011</t>
+        </is>
+      </c>
+      <c r="FK2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010100100</t>
+        </is>
+      </c>
+      <c r="FL2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100010111</t>
+        </is>
+      </c>
+      <c r="FM2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010100110</t>
+        </is>
+      </c>
+      <c r="FN2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010100111</t>
+        </is>
+      </c>
+      <c r="FO2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010101000</t>
+        </is>
+      </c>
+      <c r="FP2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010101001</t>
+        </is>
+      </c>
+      <c r="FQ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010101010</t>
+        </is>
+      </c>
+      <c r="FR2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010101011</t>
+        </is>
+      </c>
+      <c r="FS2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010101100</t>
+        </is>
+      </c>
+      <c r="FT2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010101101</t>
+        </is>
+      </c>
+      <c r="FU2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010101110</t>
+        </is>
+      </c>
+      <c r="FV2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100001001</t>
+        </is>
+      </c>
+      <c r="FW2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100010001</t>
+        </is>
+      </c>
+      <c r="FX2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100101011</t>
+        </is>
+      </c>
+      <c r="FY2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010110010</t>
+        </is>
+      </c>
+      <c r="FZ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010110011</t>
+        </is>
+      </c>
+      <c r="GA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010110100</t>
+        </is>
+      </c>
+      <c r="GB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010110101</t>
+        </is>
+      </c>
+      <c r="GC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010110110</t>
+        </is>
+      </c>
+      <c r="GD2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010110111</t>
+        </is>
+      </c>
+      <c r="GE2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010111000</t>
+        </is>
+      </c>
+      <c r="GF2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010111001</t>
+        </is>
+      </c>
+      <c r="GG2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010111010</t>
+        </is>
+      </c>
+      <c r="GH2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100100101</t>
+        </is>
+      </c>
+      <c r="GI2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010111100</t>
+        </is>
+      </c>
+      <c r="GJ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010111101</t>
+        </is>
+      </c>
+      <c r="GK2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010111110</t>
+        </is>
+      </c>
+      <c r="GL2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100100100</t>
+        </is>
+      </c>
+      <c r="GM2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011000000</t>
+        </is>
+      </c>
+      <c r="GN2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011000001</t>
+        </is>
+      </c>
+      <c r="GO2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011000010</t>
+        </is>
+      </c>
+      <c r="GP2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100001111</t>
+        </is>
+      </c>
+      <c r="GQ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011000100</t>
+        </is>
+      </c>
+      <c r="GR2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011000101</t>
+        </is>
+      </c>
+      <c r="GS2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011000110</t>
+        </is>
+      </c>
+      <c r="GT2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100100000</t>
+        </is>
+      </c>
+      <c r="GU2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100010110</t>
+        </is>
+      </c>
+      <c r="GV2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011001001</t>
+        </is>
+      </c>
+      <c r="GW2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011001010</t>
+        </is>
+      </c>
+      <c r="GX2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011001011</t>
+        </is>
+      </c>
+      <c r="GY2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011001100</t>
+        </is>
+      </c>
+      <c r="GZ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011001101</t>
+        </is>
+      </c>
+      <c r="HA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011001110</t>
+        </is>
+      </c>
+      <c r="HB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011001111</t>
+        </is>
+      </c>
+      <c r="HC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011010000</t>
+        </is>
+      </c>
+      <c r="HD2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011010001</t>
+        </is>
+      </c>
+      <c r="HE2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011010010</t>
+        </is>
+      </c>
+      <c r="HF2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100100011</t>
+        </is>
+      </c>
+      <c r="HG2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100010100</t>
+        </is>
+      </c>
+      <c r="HH2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011010101</t>
+        </is>
+      </c>
+      <c r="HI2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011010110</t>
+        </is>
+      </c>
+      <c r="HJ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100001110</t>
+        </is>
+      </c>
+      <c r="HK2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011011000</t>
+        </is>
+      </c>
+      <c r="HL2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100011101</t>
+        </is>
+      </c>
+      <c r="HM2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011011010</t>
+        </is>
+      </c>
+      <c r="HN2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011011011</t>
+        </is>
+      </c>
+      <c r="HO2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100010000</t>
+        </is>
+      </c>
+      <c r="HP2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100100010</t>
+        </is>
+      </c>
+      <c r="HQ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011011110</t>
+        </is>
+      </c>
+      <c r="HR2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011011111</t>
+        </is>
+      </c>
+      <c r="HS2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011100000</t>
+        </is>
+      </c>
+      <c r="HT2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100010101</t>
+        </is>
+      </c>
+      <c r="HU2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011100010</t>
+        </is>
+      </c>
+      <c r="HV2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011100011</t>
+        </is>
+      </c>
+      <c r="HW2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011100100</t>
+        </is>
+      </c>
+      <c r="HX2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011100101</t>
+        </is>
+      </c>
+      <c r="HY2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011100110</t>
+        </is>
+      </c>
+      <c r="HZ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011100111</t>
+        </is>
+      </c>
+      <c r="IA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011101000</t>
+        </is>
+      </c>
+      <c r="IB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011101001</t>
+        </is>
+      </c>
+      <c r="IC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011101010</t>
+        </is>
+      </c>
+      <c r="ID2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011101011</t>
+        </is>
+      </c>
+      <c r="IE2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011101100</t>
+        </is>
+      </c>
+      <c r="IF2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011101101</t>
+        </is>
+      </c>
+      <c r="IG2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100011111</t>
+        </is>
+      </c>
+      <c r="IH2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011101111</t>
+        </is>
+      </c>
+      <c r="II2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011110000</t>
+        </is>
+      </c>
+      <c r="IJ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011110001</t>
+        </is>
+      </c>
+      <c r="IK2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100001010</t>
+        </is>
+      </c>
+      <c r="IL2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011110011</t>
+        </is>
+      </c>
+      <c r="IM2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011110100</t>
+        </is>
+      </c>
+      <c r="IN2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011110101</t>
+        </is>
+      </c>
+      <c r="IO2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011110110</t>
+        </is>
+      </c>
+      <c r="IP2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011110111</t>
+        </is>
+      </c>
+      <c r="IQ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011111000</t>
+        </is>
+      </c>
+      <c r="IR2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011111001</t>
+        </is>
+      </c>
+      <c r="IS2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011111010</t>
+        </is>
+      </c>
+      <c r="IT2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011111011</t>
+        </is>
+      </c>
+      <c r="IU2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100011110</t>
+        </is>
+      </c>
+      <c r="IV2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011111101</t>
+        </is>
+      </c>
+      <c r="IW2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000011111110</t>
+        </is>
+      </c>
+      <c r="IX2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100100001</t>
+        </is>
+      </c>
+      <c r="IY2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100000000</t>
+        </is>
+      </c>
+      <c r="IZ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100100110</t>
+        </is>
+      </c>
+      <c r="JA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100000010</t>
+        </is>
+      </c>
+      <c r="JB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100000011</t>
+        </is>
+      </c>
+      <c r="JC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100000100</t>
+        </is>
+      </c>
+      <c r="JD2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000100000101</t>
+        </is>
+      </c>
+      <c r="JE2" t="inlineStr">
         <is>
           <t>00100001000100100000000000010011</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000010100</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000010101</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000010110</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000010111</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011000</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011001</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011010</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011011</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011100</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011101</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011110</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011111</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000100000</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000100001</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000100010</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000100011</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
+      <c r="JF2" t="inlineStr">
         <is>
           <t>00100001000100100000000000100100</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000100101</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000100110</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000100111</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101000</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101001</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101010</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101011</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101100</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101101</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101110</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101111</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000110000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
+      <c r="JG2" t="inlineStr">
         <is>
           <t>00100001000100100000000000110001</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="JH2" t="inlineStr">
         <is>
           <t>00100001000100100000000000110010</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000110011</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000110100</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
+      <c r="JI2" t="inlineStr">
         <is>
           <t>00100001000100100000000000110101</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000110110</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
+      <c r="JJ2" t="inlineStr">
         <is>
           <t>00100001000100100000000000110111</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111001</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111010</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111011</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111100</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111101</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111110</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111111</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000001</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000010</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000011</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000100</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000101</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000110</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000111</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001000</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001001</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001010</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001011</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001100</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001101</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001110</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001111</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001010000</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001010001</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001010010</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001010011</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001010100</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001010101</t>
-        </is>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001010110</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="JK2" t="inlineStr">
         <is>
           <t>00100001000100100000000001010111</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011000</t>
-        </is>
-      </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011001</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011010</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011011</t>
-        </is>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011100</t>
-        </is>
-      </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011101</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011110</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011111</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100000</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100001</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100010</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100011</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100100</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100101</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100110</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100111</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001101000</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001101001</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001101010</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001101011</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001101100</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
+      <c r="JL2" t="inlineStr">
         <is>
           <t>00100001000100100000000001101101</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001101110</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001101111</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001110000</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001110001</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001110010</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001110011</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001110100</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001110101</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001110110</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
+      <c r="JM2" t="inlineStr">
         <is>
           <t>00100001000100100000000001110111</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111000</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111001</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111010</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111011</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111100</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111101</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111110</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111111</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010000000</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010000001</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010000010</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010000011</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010000100</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010000101</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010000110</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010000111</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001000</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001001</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001010</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001011</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001100</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001101</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001110</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001111</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010010000</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010010001</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010010010</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010010011</t>
-        </is>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010010100</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010010101</t>
-        </is>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010010110</t>
-        </is>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010010111</t>
-        </is>
-      </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011000</t>
-        </is>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011001</t>
-        </is>
-      </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011010</t>
-        </is>
-      </c>
-      <c r="EZ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011011</t>
-        </is>
-      </c>
-      <c r="FA2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011100</t>
-        </is>
-      </c>
-      <c r="FB2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011101</t>
-        </is>
-      </c>
-      <c r="FC2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011110</t>
-        </is>
-      </c>
-      <c r="FD2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011111</t>
-        </is>
-      </c>
-      <c r="FE2" t="inlineStr">
+      <c r="JN2" t="inlineStr">
         <is>
           <t>00100001000100100000000010100000</t>
         </is>
       </c>
-      <c r="FF2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010100001</t>
-        </is>
-      </c>
-      <c r="FG2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010100010</t>
-        </is>
-      </c>
-      <c r="FH2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010100011</t>
-        </is>
-      </c>
-      <c r="FI2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010100100</t>
-        </is>
-      </c>
-      <c r="FJ2" t="inlineStr">
+      <c r="JO2" t="inlineStr">
         <is>
           <t>00100001000100100000000010100101</t>
         </is>
       </c>
-      <c r="FK2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010100110</t>
-        </is>
-      </c>
-      <c r="FL2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010100111</t>
-        </is>
-      </c>
-      <c r="FM2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010101000</t>
-        </is>
-      </c>
-      <c r="FN2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010101001</t>
-        </is>
-      </c>
-      <c r="FO2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010101010</t>
-        </is>
-      </c>
-      <c r="FP2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010101011</t>
-        </is>
-      </c>
-      <c r="FQ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010101100</t>
-        </is>
-      </c>
-      <c r="FR2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010101101</t>
-        </is>
-      </c>
-      <c r="FS2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010101110</t>
-        </is>
-      </c>
-      <c r="FT2" t="inlineStr">
+      <c r="JP2" t="inlineStr">
         <is>
           <t>00100001000100100000000010101111</t>
         </is>
       </c>
-      <c r="FU2" t="inlineStr">
+      <c r="JQ2" t="inlineStr">
         <is>
           <t>00100001000100100000000010110000</t>
         </is>
       </c>
-      <c r="FV2" t="inlineStr">
+      <c r="JR2" t="inlineStr">
         <is>
           <t>00100001000100100000000010110001</t>
         </is>
       </c>
-      <c r="FW2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010110010</t>
-        </is>
-      </c>
-      <c r="FX2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010110011</t>
-        </is>
-      </c>
-      <c r="FY2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="FZ2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GA2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GB2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GC2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GD2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GE2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GF2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GG2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GH2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GI2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GJ2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GK2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GL2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GM2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GN2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GO2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GP2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GQ2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GR2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GS2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GT2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GU2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GV2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GW2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GX2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GY2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="GZ2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HA2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HB2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HC2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HD2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HE2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HF2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HG2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HH2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HI2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HJ2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HK2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HL2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HM2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HN2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HO2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HP2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HQ2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HR2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HS2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HT2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HU2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HV2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HW2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HX2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HY2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="HZ2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IA2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IB2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IC2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="ID2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IE2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IF2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IG2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IH2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="II2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IJ2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IK2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IL2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IM2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IN2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IO2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IP2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IQ2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IR2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IS2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IT2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IU2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IV2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IW2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IX2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IY2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="IZ2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JA2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JB2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JC2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JD2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JE2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JF2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JG2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JH2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JI2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JJ2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JK2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JL2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JM2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JN2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JO2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JP2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JQ2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-      <c r="JR2" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
       <c r="JS2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000010111011</t>
         </is>
       </c>
       <c r="JT2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000010111111</t>
         </is>
       </c>
       <c r="JU2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000011000011</t>
         </is>
       </c>
       <c r="JV2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000011000111</t>
         </is>
       </c>
       <c r="JW2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000011001000</t>
         </is>
       </c>
       <c r="JX2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000011010011</t>
         </is>
       </c>
       <c r="JY2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000011010100</t>
         </is>
       </c>
       <c r="JZ2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000011010111</t>
         </is>
       </c>
       <c r="KA2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000011011001</t>
         </is>
       </c>
       <c r="KB2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000011011100</t>
         </is>
       </c>
       <c r="KC2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000011011101</t>
         </is>
       </c>
       <c r="KD2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000011100001</t>
         </is>
       </c>
       <c r="KE2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000011101110</t>
         </is>
       </c>
       <c r="KF2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000011110010</t>
         </is>
       </c>
       <c r="KG2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000011111100</t>
         </is>
       </c>
       <c r="KH2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000011111111</t>
         </is>
       </c>
       <c r="KI2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100000001</t>
         </is>
       </c>
       <c r="KJ2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100011001</t>
         </is>
       </c>
       <c r="KK2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100011010</t>
         </is>
       </c>
       <c r="KL2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100011100</t>
         </is>
       </c>
       <c r="KM2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100101000</t>
         </is>
       </c>
       <c r="KN2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100101001</t>
         </is>
       </c>
       <c r="KO2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100101100</t>
         </is>
       </c>
       <c r="KP2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100101101</t>
         </is>
       </c>
       <c r="KQ2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100101110</t>
         </is>
       </c>
       <c r="KR2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100101111</t>
         </is>
       </c>
       <c r="KS2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100110000</t>
         </is>
       </c>
       <c r="KT2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100110001</t>
         </is>
       </c>
       <c r="KU2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100110010</t>
         </is>
       </c>
       <c r="KV2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100110011</t>
         </is>
       </c>
       <c r="KW2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100110100</t>
         </is>
       </c>
       <c r="KX2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100110101</t>
         </is>
       </c>
       <c r="KY2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100110110</t>
         </is>
       </c>
       <c r="KZ2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100110111</t>
         </is>
       </c>
       <c r="LA2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100111000</t>
         </is>
       </c>
       <c r="LB2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100111001</t>
         </is>
       </c>
       <c r="LC2" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001000100100000000100111010</t>
         </is>
       </c>
       <c r="LD2" t="inlineStr">

--- a/Files/Madden26/IE/Season2/FreeAgency/Output/ContractOffer[].xlsx
+++ b/Files/Madden26/IE/Season2/FreeAgency/Output/ContractOffer[].xlsx
@@ -5098,1562 +5098,1562 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>00100001000100100000000000000011</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000000100</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000000101</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000000110</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000000111</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000001000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000001001</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000001010</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000001011</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000001100</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000001101</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000001110</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000001111</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010000</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010001</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010010</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010011</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010100</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010101</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010110</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000010111</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011000</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011001</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011010</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011011</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011100</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011101</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011110</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000011111</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100000</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100001</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100010</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100011</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100100</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100101</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100110</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000100111</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101000</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101001</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101010</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101011</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101100</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101101</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101110</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000101111</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000110000</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000110001</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000110010</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000110011</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000110100</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000110101</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000110110</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000110111</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111000</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111001</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111010</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111011</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111100</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111101</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111110</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000000111111</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000000</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000001</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000010</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000011</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000100</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000101</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000110</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001000111</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001000</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001001</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001010</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001011</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001100</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001101</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001110</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001001111</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010000</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010001</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010010</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010011</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010100</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010101</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010110</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001010111</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011000</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011001</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011010</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011011</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011100</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011101</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011110</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001011111</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100000</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100001</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100010</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100011</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100100</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100101</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100110</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001100111</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101000</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101001</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101010</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101011</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101100</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101101</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101110</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001101111</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110000</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110001</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110010</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110011</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110100</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110101</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110110</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001110111</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111000</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111001</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111010</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111011</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111100</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111101</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111110</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000001111111</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000000</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000001</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000010</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000011</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000100</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000101</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000110</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010000111</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001000</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001001</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001010</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001011</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001100</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001101</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001110</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010001111</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010010000</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010010001</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010010010</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
           <t>00100001000100100000000010010011</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000000100</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000000101</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000000110</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000000111</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011110</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011010</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000001010</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000001011</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000001100</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000001101</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000001110</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000001111</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000010000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000010001</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000010010</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001101</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000010100</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000010101</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000010110</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000010111</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011000</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011001</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="ES2" t="inlineStr">
         <is>
           <t>00100001000100100000000010010100</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011101</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011100</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011101</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001110</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011111</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000100000</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000100001</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000100010</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000100011</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001000</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000100101</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000100110</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000100111</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101000</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101001</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101010</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101011</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101100</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101101</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101111</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000110000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001010</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010010010</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000110011</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010010000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
+      <c r="ET2" t="inlineStr">
         <is>
           <t>00100001000100100000000010010101</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000110110</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010000101</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111001</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111010</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111011</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111100</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111101</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111110</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111111</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011111</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001100</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000010</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001011</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000100</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>00100001000100100000000010010110</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
         <is>
           <t>00100001000100100000000010010111</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000110</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000111</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001000</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001001</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001010</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010100001</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001100</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001101</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001110</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001111</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001010000</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000100000110</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001010010</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001111</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001010100</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001010101</t>
-        </is>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111110</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000100000111</t>
-        </is>
-      </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111100</t>
-        </is>
-      </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011001</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010000001</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011011</t>
-        </is>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011100</t>
-        </is>
-      </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011101</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011011</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010011100</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100000</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100001</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010000000</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100011</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100100</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100101</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100110</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100111</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001101000</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001101001</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010010001</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010010110</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001101100</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111011</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001101110</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001101111</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001110000</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001110001</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001110010</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001110011</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001110100</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001110101</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001110110</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000010001001</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111000</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111001</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001111010</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000000011</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000001000</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000001001</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000100001101</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011010</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011011</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000011110</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000100010011</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000101110</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000100011000</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000100100111</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000110100</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000100001100</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000100010010</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000000111101</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000000</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000001</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000011</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001000101</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001001011</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001010001</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001010011</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001010110</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000100001011</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011000</t>
-        </is>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011010</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011110</t>
-        </is>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001011111</t>
-        </is>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>00100001000100100000000001100010</t>
-        </is>
-      </c>
       <c r="EW2" t="inlineStr">
         <is>
-          <t>00100001000100100000000001101010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>00100001000100100000000001101011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100011011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100001000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>00100001000100100000000001111111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010000010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010000011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010000100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010000110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010000111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010011001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100101010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010100010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010100011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010100100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FL2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100010111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FM2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010100110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FN2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010100111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FO2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010101000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FP2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010101001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FQ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010101010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FR2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010101011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FS2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010101100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FT2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010101101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FU2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010101110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FV2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100001001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FW2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100010001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FX2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100101011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FY2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010110010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="FZ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010110011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GA2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010110100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GB2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010110101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GC2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010110110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GD2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010110111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GE2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010111000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GF2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010111001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GG2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010111010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GH2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100100101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GI2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010111100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GJ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010111101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GK2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010111110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GL2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100100100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GM2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011000000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GN2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011000001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GO2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011000010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GP2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100001111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GQ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011000100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GR2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011000101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GS2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011000110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GT2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100100000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GU2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100010110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GV2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011001001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GW2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011001010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011001011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011001100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="GZ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011001101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HA2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011001110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011001111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011010000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HD2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011010001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HE2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011010010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HF2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100100011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HG2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100010100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HH2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011010101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HI2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011010110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HJ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100001110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HK2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011011000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HL2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100011101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HM2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011011010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HN2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011011011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HO2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100010000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HP2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100100010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HQ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011011110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HR2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011011111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HS2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011100000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HT2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100010101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HU2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011100010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HV2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011100011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HW2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011100100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HX2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011100101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HY2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011100110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="HZ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011100111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IA2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011101000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IB2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011101001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IC2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011101010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="ID2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011101011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IE2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011101100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IF2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011101101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IG2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100011111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IH2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011101111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="II2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011110000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IJ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011110001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IK2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100001010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IL2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011110011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IM2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011110100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IN2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011110101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IO2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011110110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IP2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011110111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IQ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011111000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IR2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011111001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IS2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011111010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IT2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011111011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IU2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100011110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IV2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011111101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IW2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011111110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IX2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100100001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IY2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100000000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100100110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JA2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100000010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JB2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100000011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JC2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100000100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JD2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100000101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JE2" t="inlineStr">
         <is>
-          <t>00100001000100100000000000010011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JF2" t="inlineStr">
         <is>
-          <t>00100001000100100000000000100100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JG2" t="inlineStr">
         <is>
-          <t>00100001000100100000000000110001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JH2" t="inlineStr">
         <is>
-          <t>00100001000100100000000000110010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JI2" t="inlineStr">
         <is>
-          <t>00100001000100100000000000110101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JJ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000000110111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JK2" t="inlineStr">
         <is>
-          <t>00100001000100100000000001010111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JL2" t="inlineStr">
         <is>
-          <t>00100001000100100000000001101101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JM2" t="inlineStr">
         <is>
-          <t>00100001000100100000000001110111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JN2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010100000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JO2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010100101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JP2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010101111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JQ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010110000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JR2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010110001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JS2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010111011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JT2" t="inlineStr">
         <is>
-          <t>00100001000100100000000010111111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JU2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011000011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JV2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011000111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JW2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011001000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JX2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011010011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JY2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011010100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="JZ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011010111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KA2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011011001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KB2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011011100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KC2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011011101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KD2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011100001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KE2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011101110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KF2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011110010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KG2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011111100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KH2" t="inlineStr">
         <is>
-          <t>00100001000100100000000011111111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KI2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100000001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KJ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100011001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KK2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100011010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KL2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100011100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KM2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100101000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KN2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100101001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KO2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100101100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KP2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100101101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KQ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100101110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KR2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100101111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KS2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100110000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KT2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100110001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KU2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100110010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KV2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100110011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KW2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100110100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KX2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100110101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KY2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100110110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="KZ2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100110111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="LA2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100111000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="LB2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100111001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="LC2" t="inlineStr">
         <is>
-          <t>00100001000100100000000100111010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="LD2" t="inlineStr">
